--- a/software_teams.xlsx
+++ b/software_teams.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2023" uniqueCount="1229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1990" uniqueCount="1209">
   <si>
     <t>SIH 2026 — Final Teams (Software)</t>
   </si>
@@ -321,71 +321,6 @@
     <t>Electrical and Electronics Engineering · Year II · Sec B</t>
   </si>
   <si>
-    <t xml:space="preserve">ARC FORGE
-[Ministry: AICTE]
-[PS: SIH26105 (Software)]</t>
-  </si>
-  <si>
-    <t>ARAVINDHA J</t>
-  </si>
-  <si>
-    <t>25UAI019</t>
-  </si>
-  <si>
-    <t>6380143822</t>
-  </si>
-  <si>
-    <t>Artificial Intelligence and Data Science · Year II · Sec A</t>
-  </si>
-  <si>
-    <t>FATHIMA</t>
-  </si>
-  <si>
-    <t>25UAI067</t>
-  </si>
-  <si>
-    <t>9629455996</t>
-  </si>
-  <si>
-    <t>LOGHAASRI J</t>
-  </si>
-  <si>
-    <t>25UAI133</t>
-  </si>
-  <si>
-    <t>9344996575</t>
-  </si>
-  <si>
-    <t>MAGIANTUA MINI M</t>
-  </si>
-  <si>
-    <t>25UAI134</t>
-  </si>
-  <si>
-    <t>8438703967</t>
-  </si>
-  <si>
-    <t>SHAFIKA A</t>
-  </si>
-  <si>
-    <t>25UCS233</t>
-  </si>
-  <si>
-    <t>7708671531</t>
-  </si>
-  <si>
-    <t>Computer Science and Engineering · Year II · Sec E</t>
-  </si>
-  <si>
-    <t>JAYAPRIYA V</t>
-  </si>
-  <si>
-    <t>25UCS090</t>
-  </si>
-  <si>
-    <t>6374363141</t>
-  </si>
-  <si>
     <t xml:space="preserve">AstriX
 [Ministry: Qualcomm Inc]
 [PS: SIH26179 (Software)]</t>
@@ -1703,6 +1638,9 @@
     <t>7010872370</t>
   </si>
   <si>
+    <t>Artificial Intelligence and Data Science · Year II · Sec A</t>
+  </si>
+  <si>
     <t>M. SABARISH</t>
   </si>
   <si>
@@ -1728,6 +1666,68 @@
   </si>
   <si>
     <t>9789264243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECE-FINAL-291
+[Ministry: Government of Maharashtra]
+[PS: SIH26134 (Software)]</t>
+  </si>
+  <si>
+    <t>SHANTANU D</t>
+  </si>
+  <si>
+    <t>25UEC185</t>
+  </si>
+  <si>
+    <t>9994752047</t>
+  </si>
+  <si>
+    <t>VIJAY A</t>
+  </si>
+  <si>
+    <t>25UEC225</t>
+  </si>
+  <si>
+    <t>9600430181</t>
+  </si>
+  <si>
+    <t>SHREE MUNEESH</t>
+  </si>
+  <si>
+    <t>25UEC187</t>
+  </si>
+  <si>
+    <t>9629883203</t>
+  </si>
+  <si>
+    <t>SNEGA A</t>
+  </si>
+  <si>
+    <t>23UEC186</t>
+  </si>
+  <si>
+    <t>8778631463</t>
+  </si>
+  <si>
+    <t>Electronics and Communication Engineering · Year IV · Sec C</t>
+  </si>
+  <si>
+    <t>KAVITAANJALI V</t>
+  </si>
+  <si>
+    <t>23UEC089</t>
+  </si>
+  <si>
+    <t>9363735556</t>
+  </si>
+  <si>
+    <t>KOVARTHANE</t>
+  </si>
+  <si>
+    <t>24UCB029</t>
+  </si>
+  <si>
+    <t>8825523452</t>
   </si>
   <si>
     <t xml:space="preserve">ECEFINAL21
@@ -2314,9 +2314,6 @@
     <t>8608964424</t>
   </si>
   <si>
-    <t>Electronics and Communication Engineering · Year IV · Sec C</t>
-  </si>
-  <si>
     <t>ANBUMANI K</t>
   </si>
   <si>
@@ -3227,65 +3224,6 @@
   </si>
   <si>
     <t>Electronics and Communication Engineering · Year III · Sec B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SIH#IT012
-[Ministry: AICTE]
-[PS: SIH26104 (Software)]</t>
-  </si>
-  <si>
-    <t>SANJAI V</t>
-  </si>
-  <si>
-    <t>24UIT147</t>
-  </si>
-  <si>
-    <t>8270142320</t>
-  </si>
-  <si>
-    <t>HARINI M</t>
-  </si>
-  <si>
-    <t>24UIT047</t>
-  </si>
-  <si>
-    <t>7339251248</t>
-  </si>
-  <si>
-    <t>RANJITHA M</t>
-  </si>
-  <si>
-    <t>24UIT132</t>
-  </si>
-  <si>
-    <t>9344710361</t>
-  </si>
-  <si>
-    <t>KABITHA P</t>
-  </si>
-  <si>
-    <t>24UIT060</t>
-  </si>
-  <si>
-    <t>7639700282</t>
-  </si>
-  <si>
-    <t>BALA M</t>
-  </si>
-  <si>
-    <t>25UMT011</t>
-  </si>
-  <si>
-    <t>6379976258</t>
-  </si>
-  <si>
-    <t>MAGESH</t>
-  </si>
-  <si>
-    <t>25UMT034</t>
-  </si>
-  <si>
-    <t>7695898825</t>
   </si>
   <si>
     <t xml:space="preserve">SPACEX
@@ -4277,7 +4215,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I368"/>
+  <dimension ref="A1:I362"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -4913,7 +4851,7 @@
         <v>104</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
@@ -4931,10 +4869,10 @@
         <v>110</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>104</v>
+        <v>59</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H29" s="4"/>
       <c r="I29" s="4"/>
@@ -4952,10 +4890,10 @@
         <v>113</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H30" s="4"/>
       <c r="I30" s="4"/>
@@ -4964,16 +4902,16 @@
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>117</v>
+        <v>66</v>
       </c>
       <c r="G31" s="4" t="s">
         <v>30</v>
@@ -4994,7 +4932,7 @@
         <v>120</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>117</v>
+        <v>66</v>
       </c>
       <c r="G32" s="4" t="s">
         <v>30</v>
@@ -5019,10 +4957,10 @@
         <v>124</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>125</v>
+        <v>66</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H33" s="6" t="s">
         <v>16</v>
@@ -5035,19 +4973,19 @@
       <c r="A34" s="5"/>
       <c r="B34" s="5"/>
       <c r="C34" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D34" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="D34" s="6" t="s">
+      <c r="E34" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="E34" s="6" t="s">
+      <c r="F34" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="F34" s="6" t="s">
-        <v>125</v>
-      </c>
       <c r="G34" s="6" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H34" s="6"/>
       <c r="I34" s="6"/>
@@ -5065,7 +5003,7 @@
         <v>131</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>59</v>
+        <v>132</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>15</v>
@@ -5077,16 +5015,16 @@
       <c r="A36" s="5"/>
       <c r="B36" s="5"/>
       <c r="C36" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="F36" s="6" t="s">
         <v>132</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="G36" s="6" t="s">
         <v>15</v>
@@ -5107,10 +5045,10 @@
         <v>138</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H37" s="6"/>
       <c r="I37" s="6"/>
@@ -5128,10 +5066,10 @@
         <v>141</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H38" s="6"/>
       <c r="I38" s="6"/>
@@ -5153,10 +5091,10 @@
         <v>145</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>66</v>
+        <v>146</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H39" s="4" t="s">
         <v>16</v>
@@ -5169,19 +5107,19 @@
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="F40" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D40" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>149</v>
-      </c>
       <c r="G40" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
@@ -5199,7 +5137,7 @@
         <v>152</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="G41" s="4" t="s">
         <v>15</v>
@@ -5211,16 +5149,16 @@
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="D42" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="E42" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="E42" s="4" t="s">
-        <v>156</v>
-      </c>
       <c r="F42" s="4" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="G42" s="4" t="s">
         <v>15</v>
@@ -5232,19 +5170,19 @@
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="E43" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="E43" s="4" t="s">
-        <v>159</v>
-      </c>
       <c r="F43" s="4" t="s">
-        <v>153</v>
+        <v>29</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
@@ -5253,19 +5191,19 @@
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="D44" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="E44" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="E44" s="4" t="s">
-        <v>162</v>
-      </c>
       <c r="F44" s="4" t="s">
-        <v>153</v>
+        <v>29</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H44" s="4"/>
       <c r="I44" s="4"/>
@@ -5275,19 +5213,19 @@
         <v>8</v>
       </c>
       <c r="B45" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="C45" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="C45" s="6" t="s">
+      <c r="D45" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="D45" s="6" t="s">
+      <c r="E45" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="E45" s="6" t="s">
+      <c r="F45" s="6" t="s">
         <v>166</v>
-      </c>
-      <c r="F45" s="6" t="s">
-        <v>167</v>
       </c>
       <c r="G45" s="6" t="s">
         <v>15</v>
@@ -5303,19 +5241,19 @@
       <c r="A46" s="5"/>
       <c r="B46" s="5"/>
       <c r="C46" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="D46" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="D46" s="6" t="s">
+      <c r="E46" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="E46" s="6" t="s">
-        <v>170</v>
-      </c>
       <c r="F46" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H46" s="6"/>
       <c r="I46" s="6"/>
@@ -5324,16 +5262,16 @@
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
       <c r="C47" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="D47" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="D47" s="6" t="s">
+      <c r="E47" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="E47" s="6" t="s">
+      <c r="F47" s="6" t="s">
         <v>173</v>
-      </c>
-      <c r="F47" s="6" t="s">
-        <v>167</v>
       </c>
       <c r="G47" s="6" t="s">
         <v>15</v>
@@ -5354,7 +5292,7 @@
         <v>176</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="G48" s="6" t="s">
         <v>15</v>
@@ -5366,16 +5304,16 @@
       <c r="A49" s="5"/>
       <c r="B49" s="5"/>
       <c r="C49" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>29</v>
+        <v>173</v>
       </c>
       <c r="G49" s="6" t="s">
         <v>30</v>
@@ -5387,16 +5325,16 @@
       <c r="A50" s="5"/>
       <c r="B50" s="5"/>
       <c r="C50" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>29</v>
+        <v>173</v>
       </c>
       <c r="G50" s="6" t="s">
         <v>30</v>
@@ -5409,19 +5347,19 @@
         <v>9</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>187</v>
+        <v>104</v>
       </c>
       <c r="G51" s="4" t="s">
         <v>15</v>
@@ -5446,10 +5384,10 @@
         <v>190</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>187</v>
+        <v>104</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
@@ -5467,10 +5405,10 @@
         <v>193</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>194</v>
+        <v>99</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H53" s="4"/>
       <c r="I53" s="4"/>
@@ -5479,19 +5417,19 @@
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D54" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="D54" s="4" t="s">
+      <c r="E54" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="E54" s="4" t="s">
-        <v>197</v>
-      </c>
       <c r="F54" s="4" t="s">
-        <v>198</v>
+        <v>99</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H54" s="4"/>
       <c r="I54" s="4"/>
@@ -5500,16 +5438,16 @@
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="E55" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="D55" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="E55" s="4" t="s">
-        <v>201</v>
-      </c>
       <c r="F55" s="4" t="s">
-        <v>194</v>
+        <v>66</v>
       </c>
       <c r="G55" s="4" t="s">
         <v>30</v>
@@ -5521,16 +5459,16 @@
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="E56" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="D56" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="E56" s="4" t="s">
-        <v>204</v>
-      </c>
       <c r="F56" s="4" t="s">
-        <v>194</v>
+        <v>66</v>
       </c>
       <c r="G56" s="4" t="s">
         <v>30</v>
@@ -5543,22 +5481,22 @@
         <v>10</v>
       </c>
       <c r="B57" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="D57" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="C57" s="6" t="s">
+      <c r="E57" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="D57" s="6" t="s">
+      <c r="F57" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="E57" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="F57" s="6" t="s">
-        <v>125</v>
-      </c>
       <c r="G57" s="6" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H57" s="6" t="s">
         <v>16</v>
@@ -5571,19 +5509,19 @@
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="C58" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="D58" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="D58" s="6" t="s">
+      <c r="E58" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="E58" s="6" t="s">
-        <v>211</v>
-      </c>
       <c r="F58" s="6" t="s">
-        <v>125</v>
+        <v>207</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H58" s="6"/>
       <c r="I58" s="6"/>
@@ -5592,16 +5530,16 @@
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="C59" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="D59" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="D59" s="6" t="s">
+      <c r="E59" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="E59" s="6" t="s">
-        <v>214</v>
-      </c>
       <c r="F59" s="6" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G59" s="6" t="s">
         <v>30</v>
@@ -5613,19 +5551,19 @@
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="D60" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="D60" s="6" t="s">
+      <c r="E60" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="E60" s="6" t="s">
+      <c r="F60" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="F60" s="6" t="s">
-        <v>99</v>
-      </c>
       <c r="G60" s="6" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H60" s="6"/>
       <c r="I60" s="6"/>
@@ -5643,10 +5581,10 @@
         <v>220</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>66</v>
+        <v>217</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H61" s="6"/>
       <c r="I61" s="6"/>
@@ -5664,7 +5602,7 @@
         <v>223</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>66</v>
+        <v>224</v>
       </c>
       <c r="G62" s="6" t="s">
         <v>30</v>
@@ -5677,19 +5615,19 @@
         <v>11</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>228</v>
+        <v>66</v>
       </c>
       <c r="G63" s="4" t="s">
         <v>30</v>
@@ -5714,7 +5652,7 @@
         <v>231</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>228</v>
+        <v>66</v>
       </c>
       <c r="G64" s="4" t="s">
         <v>30</v>
@@ -5735,10 +5673,10 @@
         <v>234</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>125</v>
+        <v>235</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H65" s="4"/>
       <c r="I65" s="4"/>
@@ -5747,16 +5685,16 @@
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
       <c r="C66" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="F66" s="4" t="s">
         <v>235</v>
-      </c>
-      <c r="D66" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="E66" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="F66" s="4" t="s">
-        <v>238</v>
       </c>
       <c r="G66" s="4" t="s">
         <v>15</v>
@@ -5777,7 +5715,7 @@
         <v>241</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="G67" s="4" t="s">
         <v>15</v>
@@ -5789,19 +5727,19 @@
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
       <c r="C68" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>245</v>
+        <v>77</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
@@ -5823,10 +5761,10 @@
         <v>249</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="G69" s="6" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H69" s="6" t="s">
         <v>16</v>
@@ -5848,10 +5786,10 @@
         <v>252</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H70" s="6"/>
       <c r="I70" s="6"/>
@@ -5872,7 +5810,7 @@
         <v>256</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H71" s="6"/>
       <c r="I71" s="6"/>
@@ -5890,10 +5828,10 @@
         <v>259</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>256</v>
+        <v>82</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H72" s="6"/>
       <c r="I72" s="6"/>
@@ -5932,10 +5870,10 @@
         <v>266</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>77</v>
+        <v>263</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H74" s="6"/>
       <c r="I74" s="6"/>
@@ -5957,7 +5895,7 @@
         <v>270</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>73</v>
+        <v>271</v>
       </c>
       <c r="G75" s="4" t="s">
         <v>15</v>
@@ -5973,16 +5911,16 @@
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
       <c r="C76" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="F76" s="4" t="s">
         <v>271</v>
-      </c>
-      <c r="D76" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="E76" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="F76" s="4" t="s">
-        <v>73</v>
       </c>
       <c r="G76" s="4" t="s">
         <v>15</v>
@@ -5994,19 +5932,19 @@
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
       <c r="C77" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>277</v>
+        <v>73</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H77" s="4"/>
       <c r="I77" s="4"/>
@@ -6024,10 +5962,10 @@
         <v>280</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H78" s="4"/>
       <c r="I78" s="4"/>
@@ -6048,7 +5986,7 @@
         <v>284</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H79" s="4"/>
       <c r="I79" s="4"/>
@@ -6066,7 +6004,7 @@
         <v>287</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="G80" s="4" t="s">
         <v>30</v>
@@ -6079,19 +6017,19 @@
         <v>14</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>292</v>
+        <v>73</v>
       </c>
       <c r="G81" s="6" t="s">
         <v>15</v>
@@ -6116,10 +6054,10 @@
         <v>295</v>
       </c>
       <c r="F82" s="6" t="s">
-        <v>292</v>
+        <v>73</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H82" s="6"/>
       <c r="I82" s="6"/>
@@ -6137,7 +6075,7 @@
         <v>298</v>
       </c>
       <c r="F83" s="6" t="s">
-        <v>73</v>
+        <v>299</v>
       </c>
       <c r="G83" s="6" t="s">
         <v>15</v>
@@ -6149,16 +6087,16 @@
       <c r="A84" s="5"/>
       <c r="B84" s="5"/>
       <c r="C84" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>73</v>
+        <v>303</v>
       </c>
       <c r="G84" s="6" t="s">
         <v>15</v>
@@ -6170,16 +6108,16 @@
       <c r="A85" s="5"/>
       <c r="B85" s="5"/>
       <c r="C85" s="6" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>305</v>
+        <v>66</v>
       </c>
       <c r="G85" s="6" t="s">
         <v>30</v>
@@ -6191,16 +6129,16 @@
       <c r="A86" s="5"/>
       <c r="B86" s="5"/>
       <c r="C86" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F86" s="6" t="s">
-        <v>309</v>
+        <v>66</v>
       </c>
       <c r="G86" s="6" t="s">
         <v>30</v>
@@ -6228,7 +6166,7 @@
         <v>73</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H87" s="4" t="s">
         <v>16</v>
@@ -6271,7 +6209,7 @@
         <v>319</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>320</v>
+        <v>38</v>
       </c>
       <c r="G89" s="4" t="s">
         <v>15</v>
@@ -6283,16 +6221,16 @@
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
       <c r="C90" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="D90" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="D90" s="4" t="s">
+      <c r="E90" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="E90" s="4" t="s">
-        <v>323</v>
-      </c>
       <c r="F90" s="4" t="s">
-        <v>324</v>
+        <v>38</v>
       </c>
       <c r="G90" s="4" t="s">
         <v>15</v>
@@ -6304,16 +6242,16 @@
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
       <c r="C91" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="E91" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="D91" s="4" t="s">
+      <c r="F91" s="4" t="s">
         <v>326</v>
-      </c>
-      <c r="E91" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="F91" s="4" t="s">
-        <v>66</v>
       </c>
       <c r="G91" s="4" t="s">
         <v>30</v>
@@ -6325,16 +6263,16 @@
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
       <c r="C92" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="D92" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="D92" s="4" t="s">
+      <c r="E92" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="E92" s="4" t="s">
-        <v>330</v>
-      </c>
       <c r="F92" s="4" t="s">
-        <v>66</v>
+        <v>326</v>
       </c>
       <c r="G92" s="4" t="s">
         <v>30</v>
@@ -6347,19 +6285,19 @@
         <v>16</v>
       </c>
       <c r="B93" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="C93" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="C93" s="6" t="s">
+      <c r="D93" s="6" t="s">
         <v>332</v>
       </c>
-      <c r="D93" s="6" t="s">
+      <c r="E93" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="E93" s="6" t="s">
-        <v>334</v>
-      </c>
       <c r="F93" s="6" t="s">
-        <v>73</v>
+        <v>166</v>
       </c>
       <c r="G93" s="6" t="s">
         <v>30</v>
@@ -6375,16 +6313,16 @@
       <c r="A94" s="5"/>
       <c r="B94" s="5"/>
       <c r="C94" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="D94" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="D94" s="6" t="s">
+      <c r="E94" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="E94" s="6" t="s">
-        <v>337</v>
-      </c>
       <c r="F94" s="6" t="s">
-        <v>73</v>
+        <v>166</v>
       </c>
       <c r="G94" s="6" t="s">
         <v>30</v>
@@ -6396,19 +6334,19 @@
       <c r="A95" s="5"/>
       <c r="B95" s="5"/>
       <c r="C95" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="D95" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="D95" s="6" t="s">
+      <c r="E95" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="E95" s="6" t="s">
+      <c r="F95" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="F95" s="6" t="s">
-        <v>38</v>
-      </c>
       <c r="G95" s="6" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H95" s="6"/>
       <c r="I95" s="6"/>
@@ -6426,10 +6364,10 @@
         <v>343</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>38</v>
+        <v>340</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H96" s="6"/>
       <c r="I96" s="6"/>
@@ -6447,7 +6385,7 @@
         <v>346</v>
       </c>
       <c r="F97" s="6" t="s">
-        <v>347</v>
+        <v>326</v>
       </c>
       <c r="G97" s="6" t="s">
         <v>30</v>
@@ -6459,16 +6397,16 @@
       <c r="A98" s="5"/>
       <c r="B98" s="5"/>
       <c r="C98" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="D98" s="6" t="s">
         <v>348</v>
       </c>
-      <c r="D98" s="6" t="s">
+      <c r="E98" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="E98" s="6" t="s">
+      <c r="F98" s="6" t="s">
         <v>350</v>
-      </c>
-      <c r="F98" s="6" t="s">
-        <v>347</v>
       </c>
       <c r="G98" s="6" t="s">
         <v>30</v>
@@ -6493,10 +6431,10 @@
         <v>354</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>187</v>
+        <v>89</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H99" s="4" t="s">
         <v>16</v>
@@ -6518,7 +6456,7 @@
         <v>357</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>187</v>
+        <v>89</v>
       </c>
       <c r="G100" s="4" t="s">
         <v>30</v>
@@ -6581,10 +6519,10 @@
         <v>367</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>347</v>
+        <v>368</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H103" s="4"/>
       <c r="I103" s="4"/>
@@ -6593,19 +6531,19 @@
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
       <c r="C104" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="E104" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="F104" s="4" t="s">
         <v>368</v>
       </c>
-      <c r="D104" s="4" t="s">
-        <v>369</v>
-      </c>
-      <c r="E104" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="F104" s="4" t="s">
-        <v>371</v>
-      </c>
       <c r="G104" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H104" s="4"/>
       <c r="I104" s="4"/>
@@ -6627,10 +6565,10 @@
         <v>375</v>
       </c>
       <c r="F105" s="6" t="s">
-        <v>89</v>
+        <v>376</v>
       </c>
       <c r="G105" s="6" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H105" s="6" t="s">
         <v>16</v>
@@ -6643,16 +6581,16 @@
       <c r="A106" s="5"/>
       <c r="B106" s="5"/>
       <c r="C106" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G106" s="6" t="s">
         <v>30</v>
@@ -6664,19 +6602,19 @@
       <c r="A107" s="5"/>
       <c r="B107" s="5"/>
       <c r="C107" s="6" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F107" s="6" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G107" s="6" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H107" s="6"/>
       <c r="I107" s="6"/>
@@ -6685,19 +6623,19 @@
       <c r="A108" s="5"/>
       <c r="B108" s="5"/>
       <c r="C108" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="D108" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="E108" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="F108" s="6" t="s">
         <v>383</v>
       </c>
-      <c r="D108" s="6" t="s">
-        <v>384</v>
-      </c>
-      <c r="E108" s="6" t="s">
-        <v>385</v>
-      </c>
-      <c r="F108" s="6" t="s">
-        <v>382</v>
-      </c>
       <c r="G108" s="6" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H108" s="6"/>
       <c r="I108" s="6"/>
@@ -6706,16 +6644,16 @@
       <c r="A109" s="5"/>
       <c r="B109" s="5"/>
       <c r="C109" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F109" s="6" t="s">
-        <v>389</v>
+        <v>104</v>
       </c>
       <c r="G109" s="6" t="s">
         <v>15</v>
@@ -6736,7 +6674,7 @@
         <v>392</v>
       </c>
       <c r="F110" s="6" t="s">
-        <v>389</v>
+        <v>104</v>
       </c>
       <c r="G110" s="6" t="s">
         <v>15</v>
@@ -6761,7 +6699,7 @@
         <v>396</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>397</v>
+        <v>368</v>
       </c>
       <c r="G111" s="4" t="s">
         <v>30</v>
@@ -6777,16 +6715,16 @@
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
       <c r="C112" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="D112" s="4" t="s">
         <v>398</v>
       </c>
-      <c r="D112" s="4" t="s">
+      <c r="E112" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="E112" s="4" t="s">
-        <v>400</v>
-      </c>
       <c r="F112" s="4" t="s">
-        <v>77</v>
+        <v>368</v>
       </c>
       <c r="G112" s="4" t="s">
         <v>30</v>
@@ -6798,16 +6736,16 @@
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
       <c r="C113" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="D113" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="D113" s="4" t="s">
+      <c r="E113" s="4" t="s">
         <v>402</v>
       </c>
-      <c r="E113" s="4" t="s">
+      <c r="F113" s="4" t="s">
         <v>403</v>
-      </c>
-      <c r="F113" s="4" t="s">
-        <v>404</v>
       </c>
       <c r="G113" s="4" t="s">
         <v>15</v>
@@ -6819,19 +6757,19 @@
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
       <c r="C114" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="D114" s="4" t="s">
         <v>405</v>
       </c>
-      <c r="D114" s="4" t="s">
+      <c r="E114" s="4" t="s">
         <v>406</v>
       </c>
-      <c r="E114" s="4" t="s">
+      <c r="F114" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="F114" s="4" t="s">
-        <v>404</v>
-      </c>
       <c r="G114" s="4" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H114" s="4"/>
       <c r="I114" s="4"/>
@@ -6849,10 +6787,10 @@
         <v>410</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>125</v>
+        <v>166</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H115" s="4"/>
       <c r="I115" s="4"/>
@@ -6870,10 +6808,10 @@
         <v>413</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>125</v>
+        <v>368</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H116" s="4"/>
       <c r="I116" s="4"/>
@@ -6895,7 +6833,7 @@
         <v>417</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>389</v>
+        <v>368</v>
       </c>
       <c r="G117" s="6" t="s">
         <v>30</v>
@@ -6920,10 +6858,10 @@
         <v>420</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>389</v>
+        <v>368</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H118" s="6"/>
       <c r="I118" s="6"/>
@@ -6941,7 +6879,7 @@
         <v>423</v>
       </c>
       <c r="F119" s="6" t="s">
-        <v>424</v>
+        <v>368</v>
       </c>
       <c r="G119" s="6" t="s">
         <v>15</v>
@@ -6953,19 +6891,19 @@
       <c r="A120" s="5"/>
       <c r="B120" s="5"/>
       <c r="C120" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="D120" s="6" t="s">
         <v>425</v>
       </c>
-      <c r="D120" s="6" t="s">
+      <c r="E120" s="6" t="s">
         <v>426</v>
       </c>
-      <c r="E120" s="6" t="s">
-        <v>427</v>
-      </c>
       <c r="F120" s="6" t="s">
-        <v>428</v>
+        <v>73</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H120" s="6"/>
       <c r="I120" s="6"/>
@@ -6974,16 +6912,16 @@
       <c r="A121" s="5"/>
       <c r="B121" s="5"/>
       <c r="C121" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="D121" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="E121" s="6" t="s">
         <v>429</v>
       </c>
-      <c r="D121" s="6" t="s">
+      <c r="F121" s="6" t="s">
         <v>430</v>
-      </c>
-      <c r="E121" s="6" t="s">
-        <v>431</v>
-      </c>
-      <c r="F121" s="6" t="s">
-        <v>187</v>
       </c>
       <c r="G121" s="6" t="s">
         <v>30</v>
@@ -6995,16 +6933,16 @@
       <c r="A122" s="5"/>
       <c r="B122" s="5"/>
       <c r="C122" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="D122" s="6" t="s">
         <v>432</v>
       </c>
-      <c r="D122" s="6" t="s">
+      <c r="E122" s="6" t="s">
         <v>433</v>
       </c>
-      <c r="E122" s="6" t="s">
-        <v>434</v>
-      </c>
       <c r="F122" s="6" t="s">
-        <v>389</v>
+        <v>38</v>
       </c>
       <c r="G122" s="6" t="s">
         <v>30</v>
@@ -7017,19 +6955,19 @@
         <v>21</v>
       </c>
       <c r="B123" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="C123" s="4" t="s">
         <v>435</v>
       </c>
-      <c r="C123" s="4" t="s">
+      <c r="D123" s="4" t="s">
         <v>436</v>
       </c>
-      <c r="D123" s="4" t="s">
+      <c r="E123" s="4" t="s">
         <v>437</v>
       </c>
-      <c r="E123" s="4" t="s">
+      <c r="F123" s="4" t="s">
         <v>438</v>
-      </c>
-      <c r="F123" s="4" t="s">
-        <v>389</v>
       </c>
       <c r="G123" s="4" t="s">
         <v>30</v>
@@ -7054,10 +6992,10 @@
         <v>441</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>389</v>
+        <v>361</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H124" s="4"/>
       <c r="I124" s="4"/>
@@ -7075,7 +7013,7 @@
         <v>444</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>389</v>
+        <v>263</v>
       </c>
       <c r="G125" s="4" t="s">
         <v>15</v>
@@ -7096,7 +7034,7 @@
         <v>447</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>73</v>
+        <v>263</v>
       </c>
       <c r="G126" s="4" t="s">
         <v>15</v>
@@ -7138,10 +7076,10 @@
         <v>454</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>38</v>
+        <v>451</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H128" s="4"/>
       <c r="I128" s="4"/>
@@ -7166,7 +7104,7 @@
         <v>459</v>
       </c>
       <c r="G129" s="6" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H129" s="6" t="s">
         <v>16</v>
@@ -7188,7 +7126,7 @@
         <v>462</v>
       </c>
       <c r="F130" s="6" t="s">
-        <v>382</v>
+        <v>459</v>
       </c>
       <c r="G130" s="6" t="s">
         <v>30</v>
@@ -7209,7 +7147,7 @@
         <v>465</v>
       </c>
       <c r="F131" s="6" t="s">
-        <v>284</v>
+        <v>466</v>
       </c>
       <c r="G131" s="6" t="s">
         <v>15</v>
@@ -7221,19 +7159,19 @@
       <c r="A132" s="5"/>
       <c r="B132" s="5"/>
       <c r="C132" s="6" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F132" s="6" t="s">
-        <v>284</v>
+        <v>430</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H132" s="6"/>
       <c r="I132" s="6"/>
@@ -7242,16 +7180,16 @@
       <c r="A133" s="5"/>
       <c r="B133" s="5"/>
       <c r="C133" s="6" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E133" s="6" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F133" s="6" t="s">
-        <v>472</v>
+        <v>430</v>
       </c>
       <c r="G133" s="6" t="s">
         <v>30</v>
@@ -7272,7 +7210,7 @@
         <v>475</v>
       </c>
       <c r="F134" s="6" t="s">
-        <v>472</v>
+        <v>459</v>
       </c>
       <c r="G134" s="6" t="s">
         <v>15</v>
@@ -7300,7 +7238,7 @@
         <v>480</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H135" s="4" t="s">
         <v>16</v>
@@ -7343,7 +7281,7 @@
         <v>486</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>487</v>
+        <v>451</v>
       </c>
       <c r="G137" s="4" t="s">
         <v>15</v>
@@ -7355,19 +7293,19 @@
       <c r="A138" s="3"/>
       <c r="B138" s="3"/>
       <c r="C138" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="D138" s="4" t="s">
         <v>488</v>
       </c>
-      <c r="D138" s="4" t="s">
+      <c r="E138" s="4" t="s">
         <v>489</v>
-      </c>
-      <c r="E138" s="4" t="s">
-        <v>490</v>
       </c>
       <c r="F138" s="4" t="s">
         <v>451</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H138" s="4"/>
       <c r="I138" s="4"/>
@@ -7376,19 +7314,19 @@
       <c r="A139" s="3"/>
       <c r="B139" s="3"/>
       <c r="C139" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="D139" s="4" t="s">
         <v>491</v>
       </c>
-      <c r="D139" s="4" t="s">
+      <c r="E139" s="4" t="s">
         <v>492</v>
       </c>
-      <c r="E139" s="4" t="s">
-        <v>493</v>
-      </c>
       <c r="F139" s="4" t="s">
-        <v>451</v>
+        <v>430</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H139" s="4"/>
       <c r="I139" s="4"/>
@@ -7397,16 +7335,16 @@
       <c r="A140" s="3"/>
       <c r="B140" s="3"/>
       <c r="C140" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="D140" s="4" t="s">
         <v>494</v>
       </c>
-      <c r="D140" s="4" t="s">
+      <c r="E140" s="4" t="s">
         <v>495</v>
       </c>
-      <c r="E140" s="4" t="s">
-        <v>496</v>
-      </c>
       <c r="F140" s="4" t="s">
-        <v>480</v>
+        <v>430</v>
       </c>
       <c r="G140" s="4" t="s">
         <v>15</v>
@@ -7419,19 +7357,19 @@
         <v>24</v>
       </c>
       <c r="B141" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="C141" s="6" t="s">
         <v>497</v>
       </c>
-      <c r="C141" s="6" t="s">
+      <c r="D141" s="6" t="s">
         <v>498</v>
       </c>
-      <c r="D141" s="6" t="s">
+      <c r="E141" s="6" t="s">
         <v>499</v>
       </c>
-      <c r="E141" s="6" t="s">
-        <v>500</v>
-      </c>
       <c r="F141" s="6" t="s">
-        <v>501</v>
+        <v>207</v>
       </c>
       <c r="G141" s="6" t="s">
         <v>30</v>
@@ -7447,16 +7385,16 @@
       <c r="A142" s="5"/>
       <c r="B142" s="5"/>
       <c r="C142" s="6" t="s">
+        <v>500</v>
+      </c>
+      <c r="D142" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="E142" s="6" t="s">
         <v>502</v>
       </c>
-      <c r="D142" s="6" t="s">
-        <v>503</v>
-      </c>
-      <c r="E142" s="6" t="s">
-        <v>504</v>
-      </c>
       <c r="F142" s="6" t="s">
-        <v>501</v>
+        <v>207</v>
       </c>
       <c r="G142" s="6" t="s">
         <v>30</v>
@@ -7468,16 +7406,16 @@
       <c r="A143" s="5"/>
       <c r="B143" s="5"/>
       <c r="C143" s="6" t="s">
+        <v>503</v>
+      </c>
+      <c r="D143" s="6" t="s">
+        <v>504</v>
+      </c>
+      <c r="E143" s="6" t="s">
         <v>505</v>
       </c>
-      <c r="D143" s="6" t="s">
-        <v>506</v>
-      </c>
-      <c r="E143" s="6" t="s">
-        <v>507</v>
-      </c>
       <c r="F143" s="6" t="s">
-        <v>472</v>
+        <v>299</v>
       </c>
       <c r="G143" s="6" t="s">
         <v>15</v>
@@ -7489,16 +7427,16 @@
       <c r="A144" s="5"/>
       <c r="B144" s="5"/>
       <c r="C144" s="6" t="s">
+        <v>506</v>
+      </c>
+      <c r="D144" s="6" t="s">
+        <v>507</v>
+      </c>
+      <c r="E144" s="6" t="s">
         <v>508</v>
       </c>
-      <c r="D144" s="6" t="s">
-        <v>509</v>
-      </c>
-      <c r="E144" s="6" t="s">
-        <v>510</v>
-      </c>
       <c r="F144" s="6" t="s">
-        <v>472</v>
+        <v>271</v>
       </c>
       <c r="G144" s="6" t="s">
         <v>15</v>
@@ -7510,16 +7448,16 @@
       <c r="A145" s="5"/>
       <c r="B145" s="5"/>
       <c r="C145" s="6" t="s">
+        <v>509</v>
+      </c>
+      <c r="D145" s="6" t="s">
+        <v>510</v>
+      </c>
+      <c r="E145" s="6" t="s">
         <v>511</v>
       </c>
-      <c r="D145" s="6" t="s">
-        <v>512</v>
-      </c>
-      <c r="E145" s="6" t="s">
-        <v>513</v>
-      </c>
       <c r="F145" s="6" t="s">
-        <v>451</v>
+        <v>271</v>
       </c>
       <c r="G145" s="6" t="s">
         <v>15</v>
@@ -7531,19 +7469,19 @@
       <c r="A146" s="5"/>
       <c r="B146" s="5"/>
       <c r="C146" s="6" t="s">
+        <v>512</v>
+      </c>
+      <c r="D146" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="E146" s="6" t="s">
         <v>514</v>
       </c>
-      <c r="D146" s="6" t="s">
-        <v>515</v>
-      </c>
-      <c r="E146" s="6" t="s">
-        <v>516</v>
-      </c>
       <c r="F146" s="6" t="s">
-        <v>451</v>
+        <v>368</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H146" s="6"/>
       <c r="I146" s="6"/>
@@ -7553,19 +7491,19 @@
         <v>25</v>
       </c>
       <c r="B147" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="C147" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="D147" s="4" t="s">
         <v>517</v>
       </c>
-      <c r="C147" s="4" t="s">
+      <c r="E147" s="4" t="s">
         <v>518</v>
       </c>
-      <c r="D147" s="4" t="s">
-        <v>519</v>
-      </c>
-      <c r="E147" s="4" t="s">
-        <v>520</v>
-      </c>
       <c r="F147" s="4" t="s">
-        <v>228</v>
+        <v>271</v>
       </c>
       <c r="G147" s="4" t="s">
         <v>30</v>
@@ -7581,16 +7519,16 @@
       <c r="A148" s="3"/>
       <c r="B148" s="3"/>
       <c r="C148" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="D148" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="E148" s="4" t="s">
         <v>521</v>
       </c>
-      <c r="D148" s="4" t="s">
-        <v>522</v>
-      </c>
-      <c r="E148" s="4" t="s">
-        <v>523</v>
-      </c>
       <c r="F148" s="4" t="s">
-        <v>228</v>
+        <v>271</v>
       </c>
       <c r="G148" s="4" t="s">
         <v>30</v>
@@ -7602,16 +7540,16 @@
       <c r="A149" s="3"/>
       <c r="B149" s="3"/>
       <c r="C149" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="D149" s="4" t="s">
+        <v>523</v>
+      </c>
+      <c r="E149" s="4" t="s">
         <v>524</v>
       </c>
-      <c r="D149" s="4" t="s">
+      <c r="F149" s="4" t="s">
         <v>525</v>
-      </c>
-      <c r="E149" s="4" t="s">
-        <v>526</v>
-      </c>
-      <c r="F149" s="4" t="s">
-        <v>320</v>
       </c>
       <c r="G149" s="4" t="s">
         <v>15</v>
@@ -7623,16 +7561,16 @@
       <c r="A150" s="3"/>
       <c r="B150" s="3"/>
       <c r="C150" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="D150" s="4" t="s">
         <v>527</v>
       </c>
-      <c r="D150" s="4" t="s">
+      <c r="E150" s="4" t="s">
         <v>528</v>
       </c>
-      <c r="E150" s="4" t="s">
-        <v>529</v>
-      </c>
       <c r="F150" s="4" t="s">
-        <v>292</v>
+        <v>14</v>
       </c>
       <c r="G150" s="4" t="s">
         <v>15</v>
@@ -7644,16 +7582,16 @@
       <c r="A151" s="3"/>
       <c r="B151" s="3"/>
       <c r="C151" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="D151" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="D151" s="4" t="s">
+      <c r="E151" s="4" t="s">
         <v>531</v>
       </c>
-      <c r="E151" s="4" t="s">
-        <v>532</v>
-      </c>
       <c r="F151" s="4" t="s">
-        <v>292</v>
+        <v>430</v>
       </c>
       <c r="G151" s="4" t="s">
         <v>15</v>
@@ -7665,19 +7603,19 @@
       <c r="A152" s="3"/>
       <c r="B152" s="3"/>
       <c r="C152" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="D152" s="4" t="s">
         <v>533</v>
       </c>
-      <c r="D152" s="4" t="s">
+      <c r="E152" s="4" t="s">
         <v>534</v>
       </c>
-      <c r="E152" s="4" t="s">
-        <v>535</v>
-      </c>
       <c r="F152" s="4" t="s">
-        <v>389</v>
+        <v>430</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H152" s="4"/>
       <c r="I152" s="4"/>
@@ -7687,22 +7625,22 @@
         <v>26</v>
       </c>
       <c r="B153" s="5" t="s">
+        <v>535</v>
+      </c>
+      <c r="C153" s="6" t="s">
         <v>536</v>
       </c>
-      <c r="C153" s="6" t="s">
+      <c r="D153" s="6" t="s">
         <v>537</v>
       </c>
-      <c r="D153" s="6" t="s">
+      <c r="E153" s="6" t="s">
         <v>538</v>
       </c>
-      <c r="E153" s="6" t="s">
-        <v>539</v>
-      </c>
       <c r="F153" s="6" t="s">
-        <v>292</v>
+        <v>350</v>
       </c>
       <c r="G153" s="6" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H153" s="6" t="s">
         <v>16</v>
@@ -7715,19 +7653,19 @@
       <c r="A154" s="5"/>
       <c r="B154" s="5"/>
       <c r="C154" s="6" t="s">
+        <v>539</v>
+      </c>
+      <c r="D154" s="6" t="s">
         <v>540</v>
       </c>
-      <c r="D154" s="6" t="s">
+      <c r="E154" s="6" t="s">
         <v>541</v>
       </c>
-      <c r="E154" s="6" t="s">
-        <v>542</v>
-      </c>
       <c r="F154" s="6" t="s">
-        <v>292</v>
+        <v>350</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H154" s="6"/>
       <c r="I154" s="6"/>
@@ -7736,16 +7674,16 @@
       <c r="A155" s="5"/>
       <c r="B155" s="5"/>
       <c r="C155" s="6" t="s">
+        <v>542</v>
+      </c>
+      <c r="D155" s="6" t="s">
         <v>543</v>
       </c>
-      <c r="D155" s="6" t="s">
+      <c r="E155" s="6" t="s">
         <v>544</v>
       </c>
-      <c r="E155" s="6" t="s">
-        <v>545</v>
-      </c>
       <c r="F155" s="6" t="s">
-        <v>104</v>
+        <v>350</v>
       </c>
       <c r="G155" s="6" t="s">
         <v>15</v>
@@ -7757,19 +7695,19 @@
       <c r="A156" s="5"/>
       <c r="B156" s="5"/>
       <c r="C156" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="D156" s="6" t="s">
         <v>546</v>
       </c>
-      <c r="D156" s="6" t="s">
+      <c r="E156" s="6" t="s">
         <v>547</v>
       </c>
-      <c r="E156" s="6" t="s">
+      <c r="F156" s="6" t="s">
         <v>548</v>
       </c>
-      <c r="F156" s="6" t="s">
-        <v>14</v>
-      </c>
       <c r="G156" s="6" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H156" s="6"/>
       <c r="I156" s="6"/>
@@ -7787,10 +7725,10 @@
         <v>551</v>
       </c>
       <c r="F157" s="6" t="s">
-        <v>451</v>
+        <v>548</v>
       </c>
       <c r="G157" s="6" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H157" s="6"/>
       <c r="I157" s="6"/>
@@ -7808,10 +7746,10 @@
         <v>554</v>
       </c>
       <c r="F158" s="6" t="s">
-        <v>451</v>
+        <v>51</v>
       </c>
       <c r="G158" s="6" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H158" s="6"/>
       <c r="I158" s="6"/>
@@ -7833,7 +7771,7 @@
         <v>558</v>
       </c>
       <c r="F159" s="4" t="s">
-        <v>320</v>
+        <v>299</v>
       </c>
       <c r="G159" s="4" t="s">
         <v>15</v>
@@ -7858,7 +7796,7 @@
         <v>561</v>
       </c>
       <c r="F160" s="4" t="s">
-        <v>320</v>
+        <v>299</v>
       </c>
       <c r="G160" s="4" t="s">
         <v>15</v>
@@ -7921,7 +7859,7 @@
         <v>570</v>
       </c>
       <c r="F163" s="4" t="s">
-        <v>104</v>
+        <v>525</v>
       </c>
       <c r="G163" s="4" t="s">
         <v>30</v>
@@ -7942,7 +7880,7 @@
         <v>573</v>
       </c>
       <c r="F164" s="4" t="s">
-        <v>104</v>
+        <v>525</v>
       </c>
       <c r="G164" s="4" t="s">
         <v>30</v>
@@ -7967,7 +7905,7 @@
         <v>577</v>
       </c>
       <c r="F165" s="6" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
       <c r="G165" s="6" t="s">
         <v>30</v>
@@ -7992,7 +7930,7 @@
         <v>580</v>
       </c>
       <c r="F166" s="6" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
       <c r="G166" s="6" t="s">
         <v>30</v>
@@ -8013,7 +7951,7 @@
         <v>583</v>
       </c>
       <c r="F167" s="6" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
       <c r="G167" s="6" t="s">
         <v>30</v>
@@ -8034,7 +7972,7 @@
         <v>586</v>
       </c>
       <c r="F168" s="6" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="G168" s="6" t="s">
         <v>30</v>
@@ -8055,7 +7993,7 @@
         <v>589</v>
       </c>
       <c r="F169" s="6" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="G169" s="6" t="s">
         <v>15</v>
@@ -8101,7 +8039,7 @@
         <v>596</v>
       </c>
       <c r="F171" s="4" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="G171" s="4" t="s">
         <v>30</v>
@@ -8126,7 +8064,7 @@
         <v>599</v>
       </c>
       <c r="F172" s="4" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="G172" s="4" t="s">
         <v>30</v>
@@ -8147,7 +8085,7 @@
         <v>602</v>
       </c>
       <c r="F173" s="4" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="G173" s="4" t="s">
         <v>15</v>
@@ -8168,7 +8106,7 @@
         <v>605</v>
       </c>
       <c r="F174" s="4" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="G174" s="4" t="s">
         <v>15</v>
@@ -8235,7 +8173,7 @@
         <v>615</v>
       </c>
       <c r="F177" s="6" t="s">
-        <v>459</v>
+        <v>438</v>
       </c>
       <c r="G177" s="6" t="s">
         <v>30</v>
@@ -8260,7 +8198,7 @@
         <v>618</v>
       </c>
       <c r="F178" s="6" t="s">
-        <v>459</v>
+        <v>438</v>
       </c>
       <c r="G178" s="6" t="s">
         <v>30</v>
@@ -8302,7 +8240,7 @@
         <v>624</v>
       </c>
       <c r="F180" s="6" t="s">
-        <v>424</v>
+        <v>403</v>
       </c>
       <c r="G180" s="6" t="s">
         <v>30</v>
@@ -8369,7 +8307,7 @@
         <v>634</v>
       </c>
       <c r="F183" s="4" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
       <c r="G183" s="4" t="s">
         <v>15</v>
@@ -8394,7 +8332,7 @@
         <v>637</v>
       </c>
       <c r="F184" s="4" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
       <c r="G184" s="4" t="s">
         <v>15</v>
@@ -8415,7 +8353,7 @@
         <v>640</v>
       </c>
       <c r="F185" s="4" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="G185" s="4" t="s">
         <v>30</v>
@@ -8436,7 +8374,7 @@
         <v>643</v>
       </c>
       <c r="F186" s="4" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="G186" s="4" t="s">
         <v>30</v>
@@ -8457,7 +8395,7 @@
         <v>646</v>
       </c>
       <c r="F187" s="4" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="G187" s="4" t="s">
         <v>30</v>
@@ -8478,7 +8416,7 @@
         <v>649</v>
       </c>
       <c r="F188" s="4" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="G188" s="4" t="s">
         <v>30</v>
@@ -8503,7 +8441,7 @@
         <v>653</v>
       </c>
       <c r="F189" s="6" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="G189" s="6" t="s">
         <v>15</v>
@@ -8549,7 +8487,7 @@
         <v>660</v>
       </c>
       <c r="F191" s="6" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="G191" s="6" t="s">
         <v>30</v>
@@ -8570,7 +8508,7 @@
         <v>663</v>
       </c>
       <c r="F192" s="6" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="G192" s="6" t="s">
         <v>30</v>
@@ -8591,7 +8529,7 @@
         <v>666</v>
       </c>
       <c r="F193" s="6" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="G193" s="6" t="s">
         <v>30</v>
@@ -8612,7 +8550,7 @@
         <v>669</v>
       </c>
       <c r="F194" s="6" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="G194" s="6" t="s">
         <v>30</v>
@@ -8725,7 +8663,7 @@
         <v>685</v>
       </c>
       <c r="F199" s="4" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="G199" s="4" t="s">
         <v>15</v>
@@ -8746,7 +8684,7 @@
         <v>688</v>
       </c>
       <c r="F200" s="4" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="G200" s="4" t="s">
         <v>15</v>
@@ -8771,7 +8709,7 @@
         <v>692</v>
       </c>
       <c r="F201" s="6" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="G201" s="6" t="s">
         <v>30</v>
@@ -8796,7 +8734,7 @@
         <v>695</v>
       </c>
       <c r="F202" s="6" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="G202" s="6" t="s">
         <v>30</v>
@@ -8817,7 +8755,7 @@
         <v>698</v>
       </c>
       <c r="F203" s="6" t="s">
-        <v>263</v>
+        <v>242</v>
       </c>
       <c r="G203" s="6" t="s">
         <v>30</v>
@@ -8838,7 +8776,7 @@
         <v>701</v>
       </c>
       <c r="F204" s="6" t="s">
-        <v>263</v>
+        <v>242</v>
       </c>
       <c r="G204" s="6" t="s">
         <v>15</v>
@@ -8859,7 +8797,7 @@
         <v>704</v>
       </c>
       <c r="F205" s="6" t="s">
-        <v>263</v>
+        <v>242</v>
       </c>
       <c r="G205" s="6" t="s">
         <v>15</v>
@@ -8880,7 +8818,7 @@
         <v>707</v>
       </c>
       <c r="F206" s="6" t="s">
-        <v>263</v>
+        <v>242</v>
       </c>
       <c r="G206" s="6" t="s">
         <v>30</v>
@@ -9014,7 +8952,7 @@
         <v>727</v>
       </c>
       <c r="F212" s="4" t="s">
-        <v>347</v>
+        <v>326</v>
       </c>
       <c r="G212" s="4" t="s">
         <v>30</v>
@@ -9039,7 +8977,7 @@
         <v>731</v>
       </c>
       <c r="F213" s="6" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="G213" s="6" t="s">
         <v>30</v>
@@ -9064,7 +9002,7 @@
         <v>734</v>
       </c>
       <c r="F214" s="6" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="G214" s="6" t="s">
         <v>30</v>
@@ -9085,7 +9023,7 @@
         <v>737</v>
       </c>
       <c r="F215" s="6" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="G215" s="6" t="s">
         <v>30</v>
@@ -9106,7 +9044,7 @@
         <v>740</v>
       </c>
       <c r="F216" s="6" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="G216" s="6" t="s">
         <v>15</v>
@@ -9118,7 +9056,7 @@
       <c r="A217" s="5"/>
       <c r="B217" s="5"/>
       <c r="C217" s="6" t="s">
-        <v>473</v>
+        <v>452</v>
       </c>
       <c r="D217" s="6" t="s">
         <v>741</v>
@@ -9127,7 +9065,7 @@
         <v>742</v>
       </c>
       <c r="F217" s="6" t="s">
-        <v>743</v>
+        <v>548</v>
       </c>
       <c r="G217" s="6" t="s">
         <v>15</v>
@@ -9139,16 +9077,16 @@
       <c r="A218" s="5"/>
       <c r="B218" s="5"/>
       <c r="C218" s="6" t="s">
+        <v>743</v>
+      </c>
+      <c r="D218" s="6" t="s">
         <v>744</v>
       </c>
-      <c r="D218" s="6" t="s">
+      <c r="E218" s="6" t="s">
         <v>745</v>
       </c>
-      <c r="E218" s="6" t="s">
-        <v>746</v>
-      </c>
       <c r="F218" s="6" t="s">
-        <v>228</v>
+        <v>207</v>
       </c>
       <c r="G218" s="6" t="s">
         <v>15</v>
@@ -9161,19 +9099,19 @@
         <v>37</v>
       </c>
       <c r="B219" s="3" t="s">
+        <v>746</v>
+      </c>
+      <c r="C219" s="4" t="s">
         <v>747</v>
       </c>
-      <c r="C219" s="4" t="s">
+      <c r="D219" s="4" t="s">
         <v>748</v>
       </c>
-      <c r="D219" s="4" t="s">
+      <c r="E219" s="4" t="s">
         <v>749</v>
       </c>
-      <c r="E219" s="4" t="s">
-        <v>750</v>
-      </c>
       <c r="F219" s="4" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="G219" s="4" t="s">
         <v>30</v>
@@ -9189,16 +9127,16 @@
       <c r="A220" s="3"/>
       <c r="B220" s="3"/>
       <c r="C220" s="4" t="s">
+        <v>750</v>
+      </c>
+      <c r="D220" s="4" t="s">
         <v>751</v>
       </c>
-      <c r="D220" s="4" t="s">
+      <c r="E220" s="4" t="s">
         <v>752</v>
       </c>
-      <c r="E220" s="4" t="s">
-        <v>753</v>
-      </c>
       <c r="F220" s="4" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="G220" s="4" t="s">
         <v>30</v>
@@ -9210,13 +9148,13 @@
       <c r="A221" s="3"/>
       <c r="B221" s="3"/>
       <c r="C221" s="4" t="s">
+        <v>753</v>
+      </c>
+      <c r="D221" s="4" t="s">
         <v>754</v>
       </c>
-      <c r="D221" s="4" t="s">
+      <c r="E221" s="4" t="s">
         <v>755</v>
-      </c>
-      <c r="E221" s="4" t="s">
-        <v>756</v>
       </c>
       <c r="F221" s="4" t="s">
         <v>99</v>
@@ -9231,16 +9169,16 @@
       <c r="A222" s="3"/>
       <c r="B222" s="3"/>
       <c r="C222" s="4" t="s">
+        <v>756</v>
+      </c>
+      <c r="D222" s="4" t="s">
         <v>757</v>
       </c>
-      <c r="D222" s="4" t="s">
+      <c r="E222" s="4" t="s">
         <v>758</v>
       </c>
-      <c r="E222" s="4" t="s">
-        <v>759</v>
-      </c>
       <c r="F222" s="4" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="G222" s="4" t="s">
         <v>15</v>
@@ -9252,16 +9190,16 @@
       <c r="A223" s="3"/>
       <c r="B223" s="3"/>
       <c r="C223" s="4" t="s">
+        <v>759</v>
+      </c>
+      <c r="D223" s="4" t="s">
         <v>760</v>
       </c>
-      <c r="D223" s="4" t="s">
+      <c r="E223" s="4" t="s">
         <v>761</v>
       </c>
-      <c r="E223" s="4" t="s">
-        <v>762</v>
-      </c>
       <c r="F223" s="4" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="G223" s="4" t="s">
         <v>15</v>
@@ -9273,16 +9211,16 @@
       <c r="A224" s="3"/>
       <c r="B224" s="3"/>
       <c r="C224" s="4" t="s">
+        <v>762</v>
+      </c>
+      <c r="D224" s="4" t="s">
         <v>763</v>
       </c>
-      <c r="D224" s="4" t="s">
+      <c r="E224" s="4" t="s">
         <v>764</v>
       </c>
-      <c r="E224" s="4" t="s">
-        <v>765</v>
-      </c>
       <c r="F224" s="4" t="s">
-        <v>459</v>
+        <v>438</v>
       </c>
       <c r="G224" s="4" t="s">
         <v>15</v>
@@ -9295,19 +9233,19 @@
         <v>38</v>
       </c>
       <c r="B225" s="5" t="s">
+        <v>765</v>
+      </c>
+      <c r="C225" s="6" t="s">
         <v>766</v>
       </c>
-      <c r="C225" s="6" t="s">
+      <c r="D225" s="6" t="s">
         <v>767</v>
       </c>
-      <c r="D225" s="6" t="s">
+      <c r="E225" s="6" t="s">
         <v>768</v>
       </c>
-      <c r="E225" s="6" t="s">
-        <v>769</v>
-      </c>
       <c r="F225" s="6" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="G225" s="6" t="s">
         <v>30</v>
@@ -9323,16 +9261,16 @@
       <c r="A226" s="5"/>
       <c r="B226" s="5"/>
       <c r="C226" s="6" t="s">
+        <v>769</v>
+      </c>
+      <c r="D226" s="6" t="s">
         <v>770</v>
       </c>
-      <c r="D226" s="6" t="s">
+      <c r="E226" s="6" t="s">
         <v>771</v>
       </c>
-      <c r="E226" s="6" t="s">
-        <v>772</v>
-      </c>
       <c r="F226" s="6" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="G226" s="6" t="s">
         <v>30</v>
@@ -9344,16 +9282,16 @@
       <c r="A227" s="5"/>
       <c r="B227" s="5"/>
       <c r="C227" s="6" t="s">
+        <v>772</v>
+      </c>
+      <c r="D227" s="6" t="s">
         <v>773</v>
       </c>
-      <c r="D227" s="6" t="s">
+      <c r="E227" s="6" t="s">
         <v>774</v>
       </c>
-      <c r="E227" s="6" t="s">
-        <v>775</v>
-      </c>
       <c r="F227" s="6" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="G227" s="6" t="s">
         <v>30</v>
@@ -9365,16 +9303,16 @@
       <c r="A228" s="5"/>
       <c r="B228" s="5"/>
       <c r="C228" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="D228" s="6" t="s">
         <v>776</v>
       </c>
-      <c r="D228" s="6" t="s">
+      <c r="E228" s="6" t="s">
         <v>777</v>
       </c>
-      <c r="E228" s="6" t="s">
+      <c r="F228" s="6" t="s">
         <v>778</v>
-      </c>
-      <c r="F228" s="6" t="s">
-        <v>779</v>
       </c>
       <c r="G228" s="6" t="s">
         <v>15</v>
@@ -9386,16 +9324,16 @@
       <c r="A229" s="5"/>
       <c r="B229" s="5"/>
       <c r="C229" s="6" t="s">
+        <v>779</v>
+      </c>
+      <c r="D229" s="6" t="s">
         <v>780</v>
       </c>
-      <c r="D229" s="6" t="s">
+      <c r="E229" s="6" t="s">
         <v>781</v>
       </c>
-      <c r="E229" s="6" t="s">
-        <v>782</v>
-      </c>
       <c r="F229" s="6" t="s">
-        <v>743</v>
+        <v>548</v>
       </c>
       <c r="G229" s="6" t="s">
         <v>30</v>
@@ -9407,16 +9345,16 @@
       <c r="A230" s="5"/>
       <c r="B230" s="5"/>
       <c r="C230" s="6" t="s">
+        <v>782</v>
+      </c>
+      <c r="D230" s="6" t="s">
         <v>783</v>
       </c>
-      <c r="D230" s="6" t="s">
+      <c r="E230" s="6" t="s">
         <v>784</v>
       </c>
-      <c r="E230" s="6" t="s">
-        <v>785</v>
-      </c>
       <c r="F230" s="6" t="s">
-        <v>743</v>
+        <v>548</v>
       </c>
       <c r="G230" s="6" t="s">
         <v>30</v>
@@ -9429,19 +9367,19 @@
         <v>39</v>
       </c>
       <c r="B231" s="3" t="s">
+        <v>785</v>
+      </c>
+      <c r="C231" s="4" t="s">
         <v>786</v>
       </c>
-      <c r="C231" s="4" t="s">
+      <c r="D231" s="4" t="s">
         <v>787</v>
       </c>
-      <c r="D231" s="4" t="s">
+      <c r="E231" s="4" t="s">
         <v>788</v>
       </c>
-      <c r="E231" s="4" t="s">
-        <v>789</v>
-      </c>
       <c r="F231" s="4" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="G231" s="4" t="s">
         <v>30</v>
@@ -9457,16 +9395,16 @@
       <c r="A232" s="3"/>
       <c r="B232" s="3"/>
       <c r="C232" s="4" t="s">
+        <v>789</v>
+      </c>
+      <c r="D232" s="4" t="s">
         <v>790</v>
       </c>
-      <c r="D232" s="4" t="s">
+      <c r="E232" s="4" t="s">
         <v>791</v>
       </c>
-      <c r="E232" s="4" t="s">
-        <v>792</v>
-      </c>
       <c r="F232" s="4" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="G232" s="4" t="s">
         <v>30</v>
@@ -9478,16 +9416,16 @@
       <c r="A233" s="3"/>
       <c r="B233" s="3"/>
       <c r="C233" s="4" t="s">
+        <v>792</v>
+      </c>
+      <c r="D233" s="4" t="s">
         <v>793</v>
       </c>
-      <c r="D233" s="4" t="s">
+      <c r="E233" s="4" t="s">
         <v>794</v>
       </c>
-      <c r="E233" s="4" t="s">
-        <v>795</v>
-      </c>
       <c r="F233" s="4" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="G233" s="4" t="s">
         <v>15</v>
@@ -9499,16 +9437,16 @@
       <c r="A234" s="3"/>
       <c r="B234" s="3"/>
       <c r="C234" s="4" t="s">
+        <v>795</v>
+      </c>
+      <c r="D234" s="4" t="s">
         <v>796</v>
       </c>
-      <c r="D234" s="4" t="s">
+      <c r="E234" s="4" t="s">
         <v>797</v>
       </c>
-      <c r="E234" s="4" t="s">
-        <v>798</v>
-      </c>
       <c r="F234" s="4" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="G234" s="4" t="s">
         <v>15</v>
@@ -9520,16 +9458,16 @@
       <c r="A235" s="3"/>
       <c r="B235" s="3"/>
       <c r="C235" s="4" t="s">
+        <v>798</v>
+      </c>
+      <c r="D235" s="4" t="s">
         <v>799</v>
       </c>
-      <c r="D235" s="4" t="s">
+      <c r="E235" s="4" t="s">
         <v>800</v>
       </c>
-      <c r="E235" s="4" t="s">
-        <v>801</v>
-      </c>
       <c r="F235" s="4" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="G235" s="4" t="s">
         <v>15</v>
@@ -9541,16 +9479,16 @@
       <c r="A236" s="3"/>
       <c r="B236" s="3"/>
       <c r="C236" s="4" t="s">
+        <v>801</v>
+      </c>
+      <c r="D236" s="4" t="s">
         <v>802</v>
       </c>
-      <c r="D236" s="4" t="s">
+      <c r="E236" s="4" t="s">
         <v>803</v>
       </c>
-      <c r="E236" s="4" t="s">
-        <v>804</v>
-      </c>
       <c r="F236" s="4" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="G236" s="4" t="s">
         <v>15</v>
@@ -9563,19 +9501,19 @@
         <v>40</v>
       </c>
       <c r="B237" s="5" t="s">
+        <v>804</v>
+      </c>
+      <c r="C237" s="6" t="s">
         <v>805</v>
       </c>
-      <c r="C237" s="6" t="s">
+      <c r="D237" s="6" t="s">
         <v>806</v>
       </c>
-      <c r="D237" s="6" t="s">
+      <c r="E237" s="6" t="s">
         <v>807</v>
       </c>
-      <c r="E237" s="6" t="s">
-        <v>808</v>
-      </c>
       <c r="F237" s="6" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="G237" s="6" t="s">
         <v>15</v>
@@ -9591,16 +9529,16 @@
       <c r="A238" s="5"/>
       <c r="B238" s="5"/>
       <c r="C238" s="6" t="s">
+        <v>808</v>
+      </c>
+      <c r="D238" s="6" t="s">
         <v>809</v>
       </c>
-      <c r="D238" s="6" t="s">
+      <c r="E238" s="6" t="s">
         <v>810</v>
       </c>
-      <c r="E238" s="6" t="s">
-        <v>811</v>
-      </c>
       <c r="F238" s="6" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="G238" s="6" t="s">
         <v>15</v>
@@ -9612,16 +9550,16 @@
       <c r="A239" s="5"/>
       <c r="B239" s="5"/>
       <c r="C239" s="6" t="s">
+        <v>811</v>
+      </c>
+      <c r="D239" s="6" t="s">
         <v>812</v>
       </c>
-      <c r="D239" s="6" t="s">
+      <c r="E239" s="6" t="s">
         <v>813</v>
       </c>
-      <c r="E239" s="6" t="s">
-        <v>814</v>
-      </c>
       <c r="F239" s="6" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="G239" s="6" t="s">
         <v>30</v>
@@ -9633,16 +9571,16 @@
       <c r="A240" s="5"/>
       <c r="B240" s="5"/>
       <c r="C240" s="6" t="s">
+        <v>814</v>
+      </c>
+      <c r="D240" s="6" t="s">
         <v>815</v>
       </c>
-      <c r="D240" s="6" t="s">
+      <c r="E240" s="6" t="s">
         <v>816</v>
       </c>
-      <c r="E240" s="6" t="s">
-        <v>817</v>
-      </c>
       <c r="F240" s="6" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="G240" s="6" t="s">
         <v>30</v>
@@ -9654,16 +9592,16 @@
       <c r="A241" s="5"/>
       <c r="B241" s="5"/>
       <c r="C241" s="6" t="s">
+        <v>817</v>
+      </c>
+      <c r="D241" s="6" t="s">
         <v>818</v>
       </c>
-      <c r="D241" s="6" t="s">
+      <c r="E241" s="6" t="s">
         <v>819</v>
       </c>
-      <c r="E241" s="6" t="s">
-        <v>820</v>
-      </c>
       <c r="F241" s="6" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="G241" s="6" t="s">
         <v>30</v>
@@ -9675,16 +9613,16 @@
       <c r="A242" s="5"/>
       <c r="B242" s="5"/>
       <c r="C242" s="6" t="s">
+        <v>820</v>
+      </c>
+      <c r="D242" s="6" t="s">
         <v>821</v>
       </c>
-      <c r="D242" s="6" t="s">
+      <c r="E242" s="6" t="s">
         <v>822</v>
       </c>
-      <c r="E242" s="6" t="s">
-        <v>823</v>
-      </c>
       <c r="F242" s="6" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="G242" s="6" t="s">
         <v>15</v>
@@ -9697,19 +9635,19 @@
         <v>41</v>
       </c>
       <c r="B243" s="3" t="s">
+        <v>823</v>
+      </c>
+      <c r="C243" s="4" t="s">
         <v>824</v>
       </c>
-      <c r="C243" s="4" t="s">
+      <c r="D243" s="4" t="s">
         <v>825</v>
       </c>
-      <c r="D243" s="4" t="s">
+      <c r="E243" s="4" t="s">
         <v>826</v>
       </c>
-      <c r="E243" s="4" t="s">
-        <v>827</v>
-      </c>
       <c r="F243" s="4" t="s">
-        <v>284</v>
+        <v>263</v>
       </c>
       <c r="G243" s="4" t="s">
         <v>15</v>
@@ -9725,16 +9663,16 @@
       <c r="A244" s="3"/>
       <c r="B244" s="3"/>
       <c r="C244" s="4" t="s">
+        <v>827</v>
+      </c>
+      <c r="D244" s="4" t="s">
         <v>828</v>
       </c>
-      <c r="D244" s="4" t="s">
+      <c r="E244" s="4" t="s">
         <v>829</v>
       </c>
-      <c r="E244" s="4" t="s">
-        <v>830</v>
-      </c>
       <c r="F244" s="4" t="s">
-        <v>284</v>
+        <v>263</v>
       </c>
       <c r="G244" s="4" t="s">
         <v>30</v>
@@ -9746,16 +9684,16 @@
       <c r="A245" s="3"/>
       <c r="B245" s="3"/>
       <c r="C245" s="4" t="s">
+        <v>830</v>
+      </c>
+      <c r="D245" s="4" t="s">
         <v>831</v>
       </c>
-      <c r="D245" s="4" t="s">
+      <c r="E245" s="4" t="s">
         <v>832</v>
       </c>
-      <c r="E245" s="4" t="s">
-        <v>833</v>
-      </c>
       <c r="F245" s="4" t="s">
-        <v>459</v>
+        <v>438</v>
       </c>
       <c r="G245" s="4" t="s">
         <v>15</v>
@@ -9767,16 +9705,16 @@
       <c r="A246" s="3"/>
       <c r="B246" s="3"/>
       <c r="C246" s="4" t="s">
+        <v>833</v>
+      </c>
+      <c r="D246" s="4" t="s">
         <v>834</v>
       </c>
-      <c r="D246" s="4" t="s">
+      <c r="E246" s="4" t="s">
         <v>835</v>
       </c>
-      <c r="E246" s="4" t="s">
-        <v>836</v>
-      </c>
       <c r="F246" s="4" t="s">
-        <v>459</v>
+        <v>438</v>
       </c>
       <c r="G246" s="4" t="s">
         <v>15</v>
@@ -9788,16 +9726,16 @@
       <c r="A247" s="3"/>
       <c r="B247" s="3"/>
       <c r="C247" s="4" t="s">
+        <v>836</v>
+      </c>
+      <c r="D247" s="4" t="s">
         <v>837</v>
       </c>
-      <c r="D247" s="4" t="s">
+      <c r="E247" s="4" t="s">
         <v>838</v>
       </c>
-      <c r="E247" s="4" t="s">
-        <v>839</v>
-      </c>
       <c r="F247" s="4" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
       <c r="G247" s="4" t="s">
         <v>30</v>
@@ -9809,16 +9747,16 @@
       <c r="A248" s="3"/>
       <c r="B248" s="3"/>
       <c r="C248" s="4" t="s">
+        <v>839</v>
+      </c>
+      <c r="D248" s="4" t="s">
         <v>840</v>
       </c>
-      <c r="D248" s="4" t="s">
+      <c r="E248" s="4" t="s">
         <v>841</v>
       </c>
-      <c r="E248" s="4" t="s">
-        <v>842</v>
-      </c>
       <c r="F248" s="4" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
       <c r="G248" s="4" t="s">
         <v>30</v>
@@ -9831,19 +9769,19 @@
         <v>42</v>
       </c>
       <c r="B249" s="5" t="s">
+        <v>842</v>
+      </c>
+      <c r="C249" s="6" t="s">
         <v>843</v>
       </c>
-      <c r="C249" s="6" t="s">
+      <c r="D249" s="6" t="s">
         <v>844</v>
       </c>
-      <c r="D249" s="6" t="s">
+      <c r="E249" s="6" t="s">
         <v>845</v>
       </c>
-      <c r="E249" s="6" t="s">
-        <v>846</v>
-      </c>
       <c r="F249" s="6" t="s">
-        <v>228</v>
+        <v>207</v>
       </c>
       <c r="G249" s="6" t="s">
         <v>15</v>
@@ -9859,16 +9797,16 @@
       <c r="A250" s="5"/>
       <c r="B250" s="5"/>
       <c r="C250" s="6" t="s">
+        <v>846</v>
+      </c>
+      <c r="D250" s="6" t="s">
         <v>847</v>
       </c>
-      <c r="D250" s="6" t="s">
+      <c r="E250" s="6" t="s">
         <v>848</v>
       </c>
-      <c r="E250" s="6" t="s">
-        <v>849</v>
-      </c>
       <c r="F250" s="6" t="s">
-        <v>228</v>
+        <v>207</v>
       </c>
       <c r="G250" s="6" t="s">
         <v>30</v>
@@ -9880,16 +9818,16 @@
       <c r="A251" s="5"/>
       <c r="B251" s="5"/>
       <c r="C251" s="6" t="s">
+        <v>849</v>
+      </c>
+      <c r="D251" s="6" t="s">
         <v>850</v>
       </c>
-      <c r="D251" s="6" t="s">
+      <c r="E251" s="6" t="s">
         <v>851</v>
       </c>
-      <c r="E251" s="6" t="s">
-        <v>852</v>
-      </c>
       <c r="F251" s="6" t="s">
-        <v>228</v>
+        <v>207</v>
       </c>
       <c r="G251" s="6" t="s">
         <v>15</v>
@@ -9901,16 +9839,16 @@
       <c r="A252" s="5"/>
       <c r="B252" s="5"/>
       <c r="C252" s="6" t="s">
+        <v>852</v>
+      </c>
+      <c r="D252" s="6" t="s">
         <v>853</v>
       </c>
-      <c r="D252" s="6" t="s">
+      <c r="E252" s="6" t="s">
         <v>854</v>
       </c>
-      <c r="E252" s="6" t="s">
-        <v>855</v>
-      </c>
       <c r="F252" s="6" t="s">
-        <v>228</v>
+        <v>207</v>
       </c>
       <c r="G252" s="6" t="s">
         <v>15</v>
@@ -9922,13 +9860,13 @@
       <c r="A253" s="5"/>
       <c r="B253" s="5"/>
       <c r="C253" s="6" t="s">
+        <v>855</v>
+      </c>
+      <c r="D253" s="6" t="s">
         <v>856</v>
       </c>
-      <c r="D253" s="6" t="s">
+      <c r="E253" s="6" t="s">
         <v>857</v>
-      </c>
-      <c r="E253" s="6" t="s">
-        <v>858</v>
       </c>
       <c r="F253" s="6" t="s">
         <v>14</v>
@@ -9943,13 +9881,13 @@
       <c r="A254" s="5"/>
       <c r="B254" s="5"/>
       <c r="C254" s="6" t="s">
+        <v>858</v>
+      </c>
+      <c r="D254" s="6" t="s">
         <v>859</v>
       </c>
-      <c r="D254" s="6" t="s">
+      <c r="E254" s="6" t="s">
         <v>860</v>
-      </c>
-      <c r="E254" s="6" t="s">
-        <v>861</v>
       </c>
       <c r="F254" s="6" t="s">
         <v>14</v>
@@ -9965,19 +9903,19 @@
         <v>43</v>
       </c>
       <c r="B255" s="3" t="s">
+        <v>861</v>
+      </c>
+      <c r="C255" s="4" t="s">
         <v>862</v>
       </c>
-      <c r="C255" s="4" t="s">
+      <c r="D255" s="4" t="s">
         <v>863</v>
       </c>
-      <c r="D255" s="4" t="s">
+      <c r="E255" s="4" t="s">
         <v>864</v>
       </c>
-      <c r="E255" s="4" t="s">
-        <v>865</v>
-      </c>
       <c r="F255" s="4" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="G255" s="4" t="s">
         <v>30</v>
@@ -9993,16 +9931,16 @@
       <c r="A256" s="3"/>
       <c r="B256" s="3"/>
       <c r="C256" s="4" t="s">
+        <v>865</v>
+      </c>
+      <c r="D256" s="4" t="s">
         <v>866</v>
       </c>
-      <c r="D256" s="4" t="s">
+      <c r="E256" s="4" t="s">
         <v>867</v>
       </c>
-      <c r="E256" s="4" t="s">
-        <v>868</v>
-      </c>
       <c r="F256" s="4" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="G256" s="4" t="s">
         <v>30</v>
@@ -10014,16 +9952,16 @@
       <c r="A257" s="3"/>
       <c r="B257" s="3"/>
       <c r="C257" s="4" t="s">
+        <v>868</v>
+      </c>
+      <c r="D257" s="4" t="s">
         <v>869</v>
       </c>
-      <c r="D257" s="4" t="s">
+      <c r="E257" s="4" t="s">
         <v>870</v>
       </c>
-      <c r="E257" s="4" t="s">
-        <v>871</v>
-      </c>
       <c r="F257" s="4" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="G257" s="4" t="s">
         <v>30</v>
@@ -10035,16 +9973,16 @@
       <c r="A258" s="3"/>
       <c r="B258" s="3"/>
       <c r="C258" s="4" t="s">
+        <v>871</v>
+      </c>
+      <c r="D258" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="D258" s="4" t="s">
+      <c r="E258" s="4" t="s">
         <v>873</v>
       </c>
-      <c r="E258" s="4" t="s">
-        <v>874</v>
-      </c>
       <c r="F258" s="4" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="G258" s="4" t="s">
         <v>30</v>
@@ -10056,13 +9994,13 @@
       <c r="A259" s="3"/>
       <c r="B259" s="3"/>
       <c r="C259" s="4" t="s">
+        <v>874</v>
+      </c>
+      <c r="D259" s="4" t="s">
         <v>875</v>
       </c>
-      <c r="D259" s="4" t="s">
+      <c r="E259" s="4" t="s">
         <v>876</v>
-      </c>
-      <c r="E259" s="4" t="s">
-        <v>877</v>
       </c>
       <c r="F259" s="4" t="s">
         <v>77</v>
@@ -10077,16 +10015,16 @@
       <c r="A260" s="3"/>
       <c r="B260" s="3"/>
       <c r="C260" s="4" t="s">
+        <v>877</v>
+      </c>
+      <c r="D260" s="4" t="s">
         <v>878</v>
       </c>
-      <c r="D260" s="4" t="s">
+      <c r="E260" s="4" t="s">
         <v>879</v>
       </c>
-      <c r="E260" s="4" t="s">
-        <v>880</v>
-      </c>
       <c r="F260" s="4" t="s">
-        <v>187</v>
+        <v>166</v>
       </c>
       <c r="G260" s="4" t="s">
         <v>15</v>
@@ -10099,19 +10037,19 @@
         <v>44</v>
       </c>
       <c r="B261" s="5" t="s">
+        <v>880</v>
+      </c>
+      <c r="C261" s="6" t="s">
         <v>881</v>
       </c>
-      <c r="C261" s="6" t="s">
+      <c r="D261" s="6" t="s">
         <v>882</v>
       </c>
-      <c r="D261" s="6" t="s">
+      <c r="E261" s="6" t="s">
         <v>883</v>
       </c>
-      <c r="E261" s="6" t="s">
+      <c r="F261" s="6" t="s">
         <v>884</v>
-      </c>
-      <c r="F261" s="6" t="s">
-        <v>885</v>
       </c>
       <c r="G261" s="6" t="s">
         <v>30</v>
@@ -10127,16 +10065,16 @@
       <c r="A262" s="5"/>
       <c r="B262" s="5"/>
       <c r="C262" s="6" t="s">
+        <v>885</v>
+      </c>
+      <c r="D262" s="6" t="s">
         <v>886</v>
       </c>
-      <c r="D262" s="6" t="s">
+      <c r="E262" s="6" t="s">
         <v>887</v>
       </c>
-      <c r="E262" s="6" t="s">
-        <v>888</v>
-      </c>
       <c r="F262" s="6" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="G262" s="6" t="s">
         <v>30</v>
@@ -10148,16 +10086,16 @@
       <c r="A263" s="5"/>
       <c r="B263" s="5"/>
       <c r="C263" s="6" t="s">
+        <v>888</v>
+      </c>
+      <c r="D263" s="6" t="s">
         <v>889</v>
       </c>
-      <c r="D263" s="6" t="s">
+      <c r="E263" s="6" t="s">
         <v>890</v>
       </c>
-      <c r="E263" s="6" t="s">
-        <v>891</v>
-      </c>
       <c r="F263" s="6" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="G263" s="6" t="s">
         <v>30</v>
@@ -10169,16 +10107,16 @@
       <c r="A264" s="5"/>
       <c r="B264" s="5"/>
       <c r="C264" s="6" t="s">
+        <v>891</v>
+      </c>
+      <c r="D264" s="6" t="s">
         <v>892</v>
       </c>
-      <c r="D264" s="6" t="s">
+      <c r="E264" s="6" t="s">
         <v>893</v>
       </c>
-      <c r="E264" s="6" t="s">
-        <v>894</v>
-      </c>
       <c r="F264" s="6" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="G264" s="6" t="s">
         <v>30</v>
@@ -10190,13 +10128,13 @@
       <c r="A265" s="5"/>
       <c r="B265" s="5"/>
       <c r="C265" s="6" t="s">
+        <v>894</v>
+      </c>
+      <c r="D265" s="6" t="s">
         <v>895</v>
       </c>
-      <c r="D265" s="6" t="s">
+      <c r="E265" s="6" t="s">
         <v>896</v>
-      </c>
-      <c r="E265" s="6" t="s">
-        <v>897</v>
       </c>
       <c r="F265" s="6" t="s">
         <v>82</v>
@@ -10211,13 +10149,13 @@
       <c r="A266" s="5"/>
       <c r="B266" s="5"/>
       <c r="C266" s="6" t="s">
+        <v>897</v>
+      </c>
+      <c r="D266" s="6" t="s">
         <v>898</v>
       </c>
-      <c r="D266" s="6" t="s">
+      <c r="E266" s="6" t="s">
         <v>899</v>
-      </c>
-      <c r="E266" s="6" t="s">
-        <v>900</v>
       </c>
       <c r="F266" s="6" t="s">
         <v>82</v>
@@ -10233,19 +10171,19 @@
         <v>45</v>
       </c>
       <c r="B267" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="C267" s="4" t="s">
         <v>901</v>
       </c>
-      <c r="C267" s="4" t="s">
+      <c r="D267" s="4" t="s">
         <v>902</v>
       </c>
-      <c r="D267" s="4" t="s">
+      <c r="E267" s="4" t="s">
         <v>903</v>
       </c>
-      <c r="E267" s="4" t="s">
-        <v>904</v>
-      </c>
       <c r="F267" s="4" t="s">
-        <v>277</v>
+        <v>256</v>
       </c>
       <c r="G267" s="4" t="s">
         <v>15</v>
@@ -10261,16 +10199,16 @@
       <c r="A268" s="3"/>
       <c r="B268" s="3"/>
       <c r="C268" s="4" t="s">
+        <v>904</v>
+      </c>
+      <c r="D268" s="4" t="s">
         <v>905</v>
       </c>
-      <c r="D268" s="4" t="s">
+      <c r="E268" s="4" t="s">
         <v>906</v>
       </c>
-      <c r="E268" s="4" t="s">
-        <v>907</v>
-      </c>
       <c r="F268" s="4" t="s">
-        <v>320</v>
+        <v>299</v>
       </c>
       <c r="G268" s="4" t="s">
         <v>30</v>
@@ -10282,16 +10220,16 @@
       <c r="A269" s="3"/>
       <c r="B269" s="3"/>
       <c r="C269" s="4" t="s">
+        <v>907</v>
+      </c>
+      <c r="D269" s="4" t="s">
         <v>908</v>
       </c>
-      <c r="D269" s="4" t="s">
+      <c r="E269" s="4" t="s">
         <v>909</v>
       </c>
-      <c r="E269" s="4" t="s">
-        <v>910</v>
-      </c>
       <c r="F269" s="4" t="s">
-        <v>320</v>
+        <v>299</v>
       </c>
       <c r="G269" s="4" t="s">
         <v>15</v>
@@ -10303,16 +10241,16 @@
       <c r="A270" s="3"/>
       <c r="B270" s="3"/>
       <c r="C270" s="4" t="s">
+        <v>910</v>
+      </c>
+      <c r="D270" s="4" t="s">
         <v>911</v>
       </c>
-      <c r="D270" s="4" t="s">
+      <c r="E270" s="4" t="s">
         <v>912</v>
       </c>
-      <c r="E270" s="4" t="s">
+      <c r="F270" s="4" t="s">
         <v>913</v>
-      </c>
-      <c r="F270" s="4" t="s">
-        <v>914</v>
       </c>
       <c r="G270" s="4" t="s">
         <v>15</v>
@@ -10324,16 +10262,16 @@
       <c r="A271" s="3"/>
       <c r="B271" s="3"/>
       <c r="C271" s="4" t="s">
+        <v>914</v>
+      </c>
+      <c r="D271" s="4" t="s">
         <v>915</v>
       </c>
-      <c r="D271" s="4" t="s">
+      <c r="E271" s="4" t="s">
         <v>916</v>
       </c>
-      <c r="E271" s="4" t="s">
-        <v>917</v>
-      </c>
       <c r="F271" s="4" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="G271" s="4" t="s">
         <v>30</v>
@@ -10345,13 +10283,13 @@
       <c r="A272" s="3"/>
       <c r="B272" s="3"/>
       <c r="C272" s="4" t="s">
+        <v>917</v>
+      </c>
+      <c r="D272" s="4" t="s">
         <v>918</v>
       </c>
-      <c r="D272" s="4" t="s">
+      <c r="E272" s="4" t="s">
         <v>919</v>
-      </c>
-      <c r="E272" s="4" t="s">
-        <v>920</v>
       </c>
       <c r="F272" s="4" t="s">
         <v>82</v>
@@ -10367,19 +10305,19 @@
         <v>46</v>
       </c>
       <c r="B273" s="5" t="s">
+        <v>920</v>
+      </c>
+      <c r="C273" s="6" t="s">
         <v>921</v>
       </c>
-      <c r="C273" s="6" t="s">
+      <c r="D273" s="6" t="s">
         <v>922</v>
       </c>
-      <c r="D273" s="6" t="s">
+      <c r="E273" s="6" t="s">
         <v>923</v>
       </c>
-      <c r="E273" s="6" t="s">
-        <v>924</v>
-      </c>
       <c r="F273" s="6" t="s">
-        <v>292</v>
+        <v>271</v>
       </c>
       <c r="G273" s="6" t="s">
         <v>15</v>
@@ -10395,16 +10333,16 @@
       <c r="A274" s="5"/>
       <c r="B274" s="5"/>
       <c r="C274" s="6" t="s">
+        <v>924</v>
+      </c>
+      <c r="D274" s="6" t="s">
         <v>925</v>
       </c>
-      <c r="D274" s="6" t="s">
+      <c r="E274" s="6" t="s">
         <v>926</v>
       </c>
-      <c r="E274" s="6" t="s">
-        <v>927</v>
-      </c>
       <c r="F274" s="6" t="s">
-        <v>292</v>
+        <v>271</v>
       </c>
       <c r="G274" s="6" t="s">
         <v>15</v>
@@ -10416,16 +10354,16 @@
       <c r="A275" s="5"/>
       <c r="B275" s="5"/>
       <c r="C275" s="6" t="s">
+        <v>927</v>
+      </c>
+      <c r="D275" s="6" t="s">
         <v>928</v>
       </c>
-      <c r="D275" s="6" t="s">
+      <c r="E275" s="6" t="s">
         <v>929</v>
       </c>
-      <c r="E275" s="6" t="s">
+      <c r="F275" s="6" t="s">
         <v>930</v>
-      </c>
-      <c r="F275" s="6" t="s">
-        <v>931</v>
       </c>
       <c r="G275" s="6" t="s">
         <v>30</v>
@@ -10437,16 +10375,16 @@
       <c r="A276" s="5"/>
       <c r="B276" s="5"/>
       <c r="C276" s="6" t="s">
+        <v>931</v>
+      </c>
+      <c r="D276" s="6" t="s">
         <v>932</v>
       </c>
-      <c r="D276" s="6" t="s">
+      <c r="E276" s="6" t="s">
         <v>933</v>
       </c>
-      <c r="E276" s="6" t="s">
-        <v>934</v>
-      </c>
       <c r="F276" s="6" t="s">
-        <v>361</v>
+        <v>340</v>
       </c>
       <c r="G276" s="6" t="s">
         <v>30</v>
@@ -10458,16 +10396,16 @@
       <c r="A277" s="5"/>
       <c r="B277" s="5"/>
       <c r="C277" s="6" t="s">
+        <v>934</v>
+      </c>
+      <c r="D277" s="6" t="s">
         <v>935</v>
       </c>
-      <c r="D277" s="6" t="s">
+      <c r="E277" s="6" t="s">
         <v>936</v>
       </c>
-      <c r="E277" s="6" t="s">
-        <v>937</v>
-      </c>
       <c r="F277" s="6" t="s">
-        <v>361</v>
+        <v>340</v>
       </c>
       <c r="G277" s="6" t="s">
         <v>15</v>
@@ -10479,16 +10417,16 @@
       <c r="A278" s="5"/>
       <c r="B278" s="5"/>
       <c r="C278" s="6" t="s">
+        <v>937</v>
+      </c>
+      <c r="D278" s="6" t="s">
         <v>938</v>
       </c>
-      <c r="D278" s="6" t="s">
+      <c r="E278" s="6" t="s">
         <v>939</v>
       </c>
-      <c r="E278" s="6" t="s">
-        <v>940</v>
-      </c>
       <c r="F278" s="6" t="s">
-        <v>292</v>
+        <v>271</v>
       </c>
       <c r="G278" s="6" t="s">
         <v>15</v>
@@ -10501,19 +10439,19 @@
         <v>47</v>
       </c>
       <c r="B279" s="3" t="s">
+        <v>940</v>
+      </c>
+      <c r="C279" s="4" t="s">
         <v>941</v>
       </c>
-      <c r="C279" s="4" t="s">
+      <c r="D279" s="4" t="s">
         <v>942</v>
       </c>
-      <c r="D279" s="4" t="s">
+      <c r="E279" s="4" t="s">
         <v>943</v>
       </c>
-      <c r="E279" s="4" t="s">
-        <v>944</v>
-      </c>
       <c r="F279" s="4" t="s">
-        <v>104</v>
+        <v>525</v>
       </c>
       <c r="G279" s="4" t="s">
         <v>15</v>
@@ -10529,16 +10467,16 @@
       <c r="A280" s="3"/>
       <c r="B280" s="3"/>
       <c r="C280" s="4" t="s">
+        <v>944</v>
+      </c>
+      <c r="D280" s="4" t="s">
         <v>945</v>
       </c>
-      <c r="D280" s="4" t="s">
+      <c r="E280" s="4" t="s">
         <v>946</v>
       </c>
-      <c r="E280" s="4" t="s">
-        <v>947</v>
-      </c>
       <c r="F280" s="4" t="s">
-        <v>104</v>
+        <v>525</v>
       </c>
       <c r="G280" s="4" t="s">
         <v>15</v>
@@ -10550,16 +10488,16 @@
       <c r="A281" s="3"/>
       <c r="B281" s="3"/>
       <c r="C281" s="4" t="s">
+        <v>947</v>
+      </c>
+      <c r="D281" s="4" t="s">
         <v>948</v>
       </c>
-      <c r="D281" s="4" t="s">
+      <c r="E281" s="4" t="s">
         <v>949</v>
       </c>
-      <c r="E281" s="4" t="s">
-        <v>950</v>
-      </c>
       <c r="F281" s="4" t="s">
-        <v>104</v>
+        <v>525</v>
       </c>
       <c r="G281" s="4" t="s">
         <v>15</v>
@@ -10571,16 +10509,16 @@
       <c r="A282" s="3"/>
       <c r="B282" s="3"/>
       <c r="C282" s="4" t="s">
+        <v>950</v>
+      </c>
+      <c r="D282" s="4" t="s">
         <v>951</v>
       </c>
-      <c r="D282" s="4" t="s">
+      <c r="E282" s="4" t="s">
         <v>952</v>
       </c>
-      <c r="E282" s="4" t="s">
-        <v>953</v>
-      </c>
       <c r="F282" s="4" t="s">
-        <v>104</v>
+        <v>525</v>
       </c>
       <c r="G282" s="4" t="s">
         <v>15</v>
@@ -10592,16 +10530,16 @@
       <c r="A283" s="3"/>
       <c r="B283" s="3"/>
       <c r="C283" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="D283" s="4" t="s">
         <v>954</v>
       </c>
-      <c r="D283" s="4" t="s">
+      <c r="E283" s="4" t="s">
         <v>955</v>
       </c>
-      <c r="E283" s="4" t="s">
-        <v>956</v>
-      </c>
       <c r="F283" s="4" t="s">
-        <v>149</v>
+        <v>128</v>
       </c>
       <c r="G283" s="4" t="s">
         <v>30</v>
@@ -10613,16 +10551,16 @@
       <c r="A284" s="3"/>
       <c r="B284" s="3"/>
       <c r="C284" s="4" t="s">
+        <v>956</v>
+      </c>
+      <c r="D284" s="4" t="s">
         <v>957</v>
       </c>
-      <c r="D284" s="4" t="s">
+      <c r="E284" s="4" t="s">
         <v>958</v>
       </c>
-      <c r="E284" s="4" t="s">
-        <v>959</v>
-      </c>
       <c r="F284" s="4" t="s">
-        <v>149</v>
+        <v>128</v>
       </c>
       <c r="G284" s="4" t="s">
         <v>30</v>
@@ -10635,19 +10573,19 @@
         <v>48</v>
       </c>
       <c r="B285" s="5" t="s">
+        <v>959</v>
+      </c>
+      <c r="C285" s="6" t="s">
         <v>960</v>
       </c>
-      <c r="C285" s="6" t="s">
+      <c r="D285" s="6" t="s">
         <v>961</v>
       </c>
-      <c r="D285" s="6" t="s">
+      <c r="E285" s="6" t="s">
         <v>962</v>
       </c>
-      <c r="E285" s="6" t="s">
-        <v>963</v>
-      </c>
       <c r="F285" s="6" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="G285" s="6" t="s">
         <v>15</v>
@@ -10663,16 +10601,16 @@
       <c r="A286" s="5"/>
       <c r="B286" s="5"/>
       <c r="C286" s="6" t="s">
+        <v>963</v>
+      </c>
+      <c r="D286" s="6" t="s">
         <v>964</v>
       </c>
-      <c r="D286" s="6" t="s">
+      <c r="E286" s="6" t="s">
         <v>965</v>
       </c>
-      <c r="E286" s="6" t="s">
-        <v>966</v>
-      </c>
       <c r="F286" s="6" t="s">
-        <v>347</v>
+        <v>326</v>
       </c>
       <c r="G286" s="6" t="s">
         <v>15</v>
@@ -10684,13 +10622,13 @@
       <c r="A287" s="5"/>
       <c r="B287" s="5"/>
       <c r="C287" s="6" t="s">
+        <v>966</v>
+      </c>
+      <c r="D287" s="6" t="s">
         <v>967</v>
       </c>
-      <c r="D287" s="6" t="s">
+      <c r="E287" s="6" t="s">
         <v>968</v>
-      </c>
-      <c r="E287" s="6" t="s">
-        <v>969</v>
       </c>
       <c r="F287" s="6" t="s">
         <v>82</v>
@@ -10705,13 +10643,13 @@
       <c r="A288" s="5"/>
       <c r="B288" s="5"/>
       <c r="C288" s="6" t="s">
+        <v>969</v>
+      </c>
+      <c r="D288" s="6" t="s">
         <v>970</v>
       </c>
-      <c r="D288" s="6" t="s">
+      <c r="E288" s="6" t="s">
         <v>971</v>
-      </c>
-      <c r="E288" s="6" t="s">
-        <v>972</v>
       </c>
       <c r="F288" s="6" t="s">
         <v>82</v>
@@ -10726,16 +10664,16 @@
       <c r="A289" s="5"/>
       <c r="B289" s="5"/>
       <c r="C289" s="6" t="s">
+        <v>972</v>
+      </c>
+      <c r="D289" s="6" t="s">
         <v>973</v>
       </c>
-      <c r="D289" s="6" t="s">
+      <c r="E289" s="6" t="s">
         <v>974</v>
       </c>
-      <c r="E289" s="6" t="s">
-        <v>975</v>
-      </c>
       <c r="F289" s="6" t="s">
-        <v>382</v>
+        <v>361</v>
       </c>
       <c r="G289" s="6" t="s">
         <v>30</v>
@@ -10747,16 +10685,16 @@
       <c r="A290" s="5"/>
       <c r="B290" s="5"/>
       <c r="C290" s="6" t="s">
+        <v>975</v>
+      </c>
+      <c r="D290" s="6" t="s">
         <v>976</v>
       </c>
-      <c r="D290" s="6" t="s">
+      <c r="E290" s="6" t="s">
         <v>977</v>
       </c>
-      <c r="E290" s="6" t="s">
-        <v>978</v>
-      </c>
       <c r="F290" s="6" t="s">
-        <v>459</v>
+        <v>438</v>
       </c>
       <c r="G290" s="6" t="s">
         <v>30</v>
@@ -10769,19 +10707,19 @@
         <v>49</v>
       </c>
       <c r="B291" s="3" t="s">
+        <v>978</v>
+      </c>
+      <c r="C291" s="4" t="s">
         <v>979</v>
       </c>
-      <c r="C291" s="4" t="s">
+      <c r="D291" s="4" t="s">
         <v>980</v>
       </c>
-      <c r="D291" s="4" t="s">
+      <c r="E291" s="4" t="s">
         <v>981</v>
       </c>
-      <c r="E291" s="4" t="s">
+      <c r="F291" s="4" t="s">
         <v>982</v>
-      </c>
-      <c r="F291" s="4" t="s">
-        <v>983</v>
       </c>
       <c r="G291" s="4" t="s">
         <v>30</v>
@@ -10797,16 +10735,16 @@
       <c r="A292" s="3"/>
       <c r="B292" s="3"/>
       <c r="C292" s="4" t="s">
+        <v>983</v>
+      </c>
+      <c r="D292" s="4" t="s">
         <v>984</v>
       </c>
-      <c r="D292" s="4" t="s">
+      <c r="E292" s="4" t="s">
         <v>985</v>
       </c>
-      <c r="E292" s="4" t="s">
-        <v>986</v>
-      </c>
       <c r="F292" s="4" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="G292" s="4" t="s">
         <v>30</v>
@@ -10818,16 +10756,16 @@
       <c r="A293" s="3"/>
       <c r="B293" s="3"/>
       <c r="C293" s="4" t="s">
+        <v>986</v>
+      </c>
+      <c r="D293" s="4" t="s">
         <v>987</v>
       </c>
-      <c r="D293" s="4" t="s">
+      <c r="E293" s="4" t="s">
         <v>988</v>
       </c>
-      <c r="E293" s="4" t="s">
-        <v>989</v>
-      </c>
       <c r="F293" s="4" t="s">
-        <v>451</v>
+        <v>430</v>
       </c>
       <c r="G293" s="4" t="s">
         <v>15</v>
@@ -10839,16 +10777,16 @@
       <c r="A294" s="3"/>
       <c r="B294" s="3"/>
       <c r="C294" s="4" t="s">
+        <v>989</v>
+      </c>
+      <c r="D294" s="4" t="s">
         <v>990</v>
       </c>
-      <c r="D294" s="4" t="s">
+      <c r="E294" s="4" t="s">
         <v>991</v>
       </c>
-      <c r="E294" s="4" t="s">
-        <v>992</v>
-      </c>
       <c r="F294" s="4" t="s">
-        <v>451</v>
+        <v>430</v>
       </c>
       <c r="G294" s="4" t="s">
         <v>15</v>
@@ -10860,16 +10798,16 @@
       <c r="A295" s="3"/>
       <c r="B295" s="3"/>
       <c r="C295" s="4" t="s">
+        <v>992</v>
+      </c>
+      <c r="D295" s="4" t="s">
         <v>993</v>
       </c>
-      <c r="D295" s="4" t="s">
+      <c r="E295" s="4" t="s">
         <v>994</v>
       </c>
-      <c r="E295" s="4" t="s">
-        <v>995</v>
-      </c>
       <c r="F295" s="4" t="s">
-        <v>284</v>
+        <v>263</v>
       </c>
       <c r="G295" s="4" t="s">
         <v>15</v>
@@ -10881,16 +10819,16 @@
       <c r="A296" s="3"/>
       <c r="B296" s="3"/>
       <c r="C296" s="4" t="s">
+        <v>995</v>
+      </c>
+      <c r="D296" s="4" t="s">
         <v>996</v>
       </c>
-      <c r="D296" s="4" t="s">
+      <c r="E296" s="4" t="s">
         <v>997</v>
       </c>
-      <c r="E296" s="4" t="s">
-        <v>998</v>
-      </c>
       <c r="F296" s="4" t="s">
-        <v>284</v>
+        <v>263</v>
       </c>
       <c r="G296" s="4" t="s">
         <v>15</v>
@@ -10903,19 +10841,19 @@
         <v>50</v>
       </c>
       <c r="B297" s="5" t="s">
+        <v>998</v>
+      </c>
+      <c r="C297" s="6" t="s">
         <v>999</v>
       </c>
-      <c r="C297" s="6" t="s">
+      <c r="D297" s="6" t="s">
         <v>1000</v>
       </c>
-      <c r="D297" s="6" t="s">
+      <c r="E297" s="6" t="s">
         <v>1001</v>
       </c>
-      <c r="E297" s="6" t="s">
-        <v>1002</v>
-      </c>
       <c r="F297" s="6" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="G297" s="6" t="s">
         <v>30</v>
@@ -10931,16 +10869,16 @@
       <c r="A298" s="5"/>
       <c r="B298" s="5"/>
       <c r="C298" s="6" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D298" s="6" t="s">
         <v>1003</v>
       </c>
-      <c r="D298" s="6" t="s">
+      <c r="E298" s="6" t="s">
         <v>1004</v>
       </c>
-      <c r="E298" s="6" t="s">
-        <v>1005</v>
-      </c>
       <c r="F298" s="6" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="G298" s="6" t="s">
         <v>30</v>
@@ -10952,16 +10890,16 @@
       <c r="A299" s="5"/>
       <c r="B299" s="5"/>
       <c r="C299" s="6" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D299" s="6" t="s">
         <v>1006</v>
       </c>
-      <c r="D299" s="6" t="s">
+      <c r="E299" s="6" t="s">
         <v>1007</v>
       </c>
-      <c r="E299" s="6" t="s">
-        <v>1008</v>
-      </c>
       <c r="F299" s="6" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="G299" s="6" t="s">
         <v>15</v>
@@ -10973,16 +10911,16 @@
       <c r="A300" s="5"/>
       <c r="B300" s="5"/>
       <c r="C300" s="6" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D300" s="6" t="s">
         <v>1009</v>
       </c>
-      <c r="D300" s="6" t="s">
+      <c r="E300" s="6" t="s">
         <v>1010</v>
       </c>
-      <c r="E300" s="6" t="s">
-        <v>1011</v>
-      </c>
       <c r="F300" s="6" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="G300" s="6" t="s">
         <v>15</v>
@@ -10994,16 +10932,16 @@
       <c r="A301" s="5"/>
       <c r="B301" s="5"/>
       <c r="C301" s="6" t="s">
+        <v>1011</v>
+      </c>
+      <c r="D301" s="6" t="s">
         <v>1012</v>
       </c>
-      <c r="D301" s="6" t="s">
+      <c r="E301" s="6" t="s">
         <v>1013</v>
       </c>
-      <c r="E301" s="6" t="s">
-        <v>1014</v>
-      </c>
       <c r="F301" s="6" t="s">
-        <v>277</v>
+        <v>256</v>
       </c>
       <c r="G301" s="6" t="s">
         <v>15</v>
@@ -11015,16 +10953,16 @@
       <c r="A302" s="5"/>
       <c r="B302" s="5"/>
       <c r="C302" s="6" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D302" s="6" t="s">
         <v>1015</v>
       </c>
-      <c r="D302" s="6" t="s">
+      <c r="E302" s="6" t="s">
         <v>1016</v>
       </c>
-      <c r="E302" s="6" t="s">
-        <v>1017</v>
-      </c>
       <c r="F302" s="6" t="s">
-        <v>428</v>
+        <v>407</v>
       </c>
       <c r="G302" s="6" t="s">
         <v>15</v>
@@ -11037,19 +10975,19 @@
         <v>51</v>
       </c>
       <c r="B303" s="3" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C303" s="4" t="s">
         <v>1018</v>
       </c>
-      <c r="C303" s="4" t="s">
+      <c r="D303" s="4" t="s">
         <v>1019</v>
       </c>
-      <c r="D303" s="4" t="s">
+      <c r="E303" s="4" t="s">
         <v>1020</v>
       </c>
-      <c r="E303" s="4" t="s">
-        <v>1021</v>
-      </c>
       <c r="F303" s="4" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="G303" s="4" t="s">
         <v>15</v>
@@ -11065,16 +11003,16 @@
       <c r="A304" s="3"/>
       <c r="B304" s="3"/>
       <c r="C304" s="4" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D304" s="4" t="s">
         <v>1022</v>
       </c>
-      <c r="D304" s="4" t="s">
+      <c r="E304" s="4" t="s">
         <v>1023</v>
       </c>
-      <c r="E304" s="4" t="s">
-        <v>1024</v>
-      </c>
       <c r="F304" s="4" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="G304" s="4" t="s">
         <v>30</v>
@@ -11086,16 +11024,16 @@
       <c r="A305" s="3"/>
       <c r="B305" s="3"/>
       <c r="C305" s="4" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D305" s="4" t="s">
         <v>1025</v>
       </c>
-      <c r="D305" s="4" t="s">
+      <c r="E305" s="4" t="s">
         <v>1026</v>
       </c>
-      <c r="E305" s="4" t="s">
-        <v>1027</v>
-      </c>
       <c r="F305" s="4" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="G305" s="4" t="s">
         <v>15</v>
@@ -11107,16 +11045,16 @@
       <c r="A306" s="3"/>
       <c r="B306" s="3"/>
       <c r="C306" s="4" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D306" s="4" t="s">
         <v>1028</v>
       </c>
-      <c r="D306" s="4" t="s">
+      <c r="E306" s="4" t="s">
         <v>1029</v>
       </c>
-      <c r="E306" s="4" t="s">
-        <v>1030</v>
-      </c>
       <c r="F306" s="4" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="G306" s="4" t="s">
         <v>15</v>
@@ -11128,16 +11066,16 @@
       <c r="A307" s="3"/>
       <c r="B307" s="3"/>
       <c r="C307" s="4" t="s">
+        <v>1030</v>
+      </c>
+      <c r="D307" s="4" t="s">
         <v>1031</v>
       </c>
-      <c r="D307" s="4" t="s">
+      <c r="E307" s="4" t="s">
         <v>1032</v>
       </c>
-      <c r="E307" s="4" t="s">
-        <v>1033</v>
-      </c>
       <c r="F307" s="4" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="G307" s="4" t="s">
         <v>15</v>
@@ -11149,16 +11087,16 @@
       <c r="A308" s="3"/>
       <c r="B308" s="3"/>
       <c r="C308" s="4" t="s">
+        <v>1033</v>
+      </c>
+      <c r="D308" s="4" t="s">
         <v>1034</v>
       </c>
-      <c r="D308" s="4" t="s">
+      <c r="E308" s="4" t="s">
         <v>1035</v>
       </c>
-      <c r="E308" s="4" t="s">
+      <c r="F308" s="4" t="s">
         <v>1036</v>
-      </c>
-      <c r="F308" s="4" t="s">
-        <v>1037</v>
       </c>
       <c r="G308" s="4" t="s">
         <v>30</v>
@@ -11171,19 +11109,19 @@
         <v>52</v>
       </c>
       <c r="B309" s="5" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C309" s="6" t="s">
         <v>1038</v>
       </c>
-      <c r="C309" s="6" t="s">
+      <c r="D309" s="6" t="s">
         <v>1039</v>
       </c>
-      <c r="D309" s="6" t="s">
+      <c r="E309" s="6" t="s">
         <v>1040</v>
       </c>
-      <c r="E309" s="6" t="s">
-        <v>1041</v>
-      </c>
       <c r="F309" s="6" t="s">
-        <v>263</v>
+        <v>480</v>
       </c>
       <c r="G309" s="6" t="s">
         <v>15</v>
@@ -11199,19 +11137,19 @@
       <c r="A310" s="5"/>
       <c r="B310" s="5"/>
       <c r="C310" s="6" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D310" s="6" t="s">
         <v>1042</v>
       </c>
-      <c r="D310" s="6" t="s">
+      <c r="E310" s="6" t="s">
         <v>1043</v>
       </c>
-      <c r="E310" s="6" t="s">
-        <v>1044</v>
-      </c>
       <c r="F310" s="6" t="s">
-        <v>263</v>
+        <v>480</v>
       </c>
       <c r="G310" s="6" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H310" s="6"/>
       <c r="I310" s="6"/>
@@ -11220,16 +11158,16 @@
       <c r="A311" s="5"/>
       <c r="B311" s="5"/>
       <c r="C311" s="6" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D311" s="6" t="s">
         <v>1045</v>
       </c>
-      <c r="D311" s="6" t="s">
+      <c r="E311" s="6" t="s">
         <v>1046</v>
       </c>
-      <c r="E311" s="6" t="s">
-        <v>1047</v>
-      </c>
       <c r="F311" s="6" t="s">
-        <v>263</v>
+        <v>451</v>
       </c>
       <c r="G311" s="6" t="s">
         <v>30</v>
@@ -11241,16 +11179,16 @@
       <c r="A312" s="5"/>
       <c r="B312" s="5"/>
       <c r="C312" s="6" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D312" s="6" t="s">
         <v>1048</v>
       </c>
-      <c r="D312" s="6" t="s">
+      <c r="E312" s="6" t="s">
         <v>1049</v>
       </c>
-      <c r="E312" s="6" t="s">
-        <v>1050</v>
-      </c>
       <c r="F312" s="6" t="s">
-        <v>263</v>
+        <v>451</v>
       </c>
       <c r="G312" s="6" t="s">
         <v>30</v>
@@ -11262,16 +11200,16 @@
       <c r="A313" s="5"/>
       <c r="B313" s="5"/>
       <c r="C313" s="6" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D313" s="6" t="s">
         <v>1051</v>
       </c>
-      <c r="D313" s="6" t="s">
+      <c r="E313" s="6" t="s">
         <v>1052</v>
       </c>
-      <c r="E313" s="6" t="s">
-        <v>1053</v>
-      </c>
       <c r="F313" s="6" t="s">
-        <v>404</v>
+        <v>104</v>
       </c>
       <c r="G313" s="6" t="s">
         <v>15</v>
@@ -11283,16 +11221,16 @@
       <c r="A314" s="5"/>
       <c r="B314" s="5"/>
       <c r="C314" s="6" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D314" s="6" t="s">
         <v>1054</v>
       </c>
-      <c r="D314" s="6" t="s">
+      <c r="E314" s="6" t="s">
         <v>1055</v>
       </c>
-      <c r="E314" s="6" t="s">
-        <v>1056</v>
-      </c>
       <c r="F314" s="6" t="s">
-        <v>404</v>
+        <v>104</v>
       </c>
       <c r="G314" s="6" t="s">
         <v>15</v>
@@ -11305,22 +11243,22 @@
         <v>53</v>
       </c>
       <c r="B315" s="3" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C315" s="4" t="s">
         <v>1057</v>
       </c>
-      <c r="C315" s="4" t="s">
+      <c r="D315" s="4" t="s">
         <v>1058</v>
       </c>
-      <c r="D315" s="4" t="s">
+      <c r="E315" s="4" t="s">
         <v>1059</v>
       </c>
-      <c r="E315" s="4" t="s">
-        <v>1060</v>
-      </c>
       <c r="F315" s="4" t="s">
-        <v>501</v>
+        <v>712</v>
       </c>
       <c r="G315" s="4" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H315" s="4" t="s">
         <v>16</v>
@@ -11333,19 +11271,19 @@
       <c r="A316" s="3"/>
       <c r="B316" s="3"/>
       <c r="C316" s="4" t="s">
+        <v>1060</v>
+      </c>
+      <c r="D316" s="4" t="s">
         <v>1061</v>
       </c>
-      <c r="D316" s="4" t="s">
+      <c r="E316" s="4" t="s">
         <v>1062</v>
       </c>
-      <c r="E316" s="4" t="s">
-        <v>1063</v>
-      </c>
       <c r="F316" s="4" t="s">
-        <v>501</v>
+        <v>712</v>
       </c>
       <c r="G316" s="4" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H316" s="4"/>
       <c r="I316" s="4"/>
@@ -11354,19 +11292,19 @@
       <c r="A317" s="3"/>
       <c r="B317" s="3"/>
       <c r="C317" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D317" s="4" t="s">
         <v>1064</v>
       </c>
-      <c r="D317" s="4" t="s">
+      <c r="E317" s="4" t="s">
         <v>1065</v>
       </c>
-      <c r="E317" s="4" t="s">
-        <v>1066</v>
-      </c>
       <c r="F317" s="4" t="s">
-        <v>472</v>
+        <v>712</v>
       </c>
       <c r="G317" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H317" s="4"/>
       <c r="I317" s="4"/>
@@ -11375,19 +11313,19 @@
       <c r="A318" s="3"/>
       <c r="B318" s="3"/>
       <c r="C318" s="4" t="s">
+        <v>1066</v>
+      </c>
+      <c r="D318" s="4" t="s">
         <v>1067</v>
       </c>
-      <c r="D318" s="4" t="s">
+      <c r="E318" s="4" t="s">
         <v>1068</v>
       </c>
-      <c r="E318" s="4" t="s">
-        <v>1069</v>
-      </c>
       <c r="F318" s="4" t="s">
-        <v>472</v>
+        <v>712</v>
       </c>
       <c r="G318" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H318" s="4"/>
       <c r="I318" s="4"/>
@@ -11396,19 +11334,19 @@
       <c r="A319" s="3"/>
       <c r="B319" s="3"/>
       <c r="C319" s="4" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D319" s="4" t="s">
         <v>1070</v>
       </c>
-      <c r="D319" s="4" t="s">
+      <c r="E319" s="4" t="s">
         <v>1071</v>
       </c>
-      <c r="E319" s="4" t="s">
-        <v>1072</v>
-      </c>
       <c r="F319" s="4" t="s">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="G319" s="4" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H319" s="4"/>
       <c r="I319" s="4"/>
@@ -11417,19 +11355,19 @@
       <c r="A320" s="3"/>
       <c r="B320" s="3"/>
       <c r="C320" s="4" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D320" s="4" t="s">
         <v>1073</v>
       </c>
-      <c r="D320" s="4" t="s">
+      <c r="E320" s="4" t="s">
         <v>1074</v>
       </c>
-      <c r="E320" s="4" t="s">
-        <v>1075</v>
-      </c>
       <c r="F320" s="4" t="s">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="G320" s="4" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H320" s="4"/>
       <c r="I320" s="4"/>
@@ -11439,22 +11377,22 @@
         <v>54</v>
       </c>
       <c r="B321" s="5" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C321" s="6" t="s">
         <v>1076</v>
       </c>
-      <c r="C321" s="6" t="s">
+      <c r="D321" s="6" t="s">
         <v>1077</v>
       </c>
-      <c r="D321" s="6" t="s">
+      <c r="E321" s="6" t="s">
         <v>1078</v>
       </c>
-      <c r="E321" s="6" t="s">
-        <v>1079</v>
-      </c>
       <c r="F321" s="6" t="s">
-        <v>712</v>
+        <v>982</v>
       </c>
       <c r="G321" s="6" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H321" s="6" t="s">
         <v>16</v>
@@ -11467,19 +11405,19 @@
       <c r="A322" s="5"/>
       <c r="B322" s="5"/>
       <c r="C322" s="6" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D322" s="6" t="s">
         <v>1080</v>
       </c>
-      <c r="D322" s="6" t="s">
+      <c r="E322" s="6" t="s">
         <v>1081</v>
       </c>
-      <c r="E322" s="6" t="s">
-        <v>1082</v>
-      </c>
       <c r="F322" s="6" t="s">
-        <v>712</v>
+        <v>982</v>
       </c>
       <c r="G322" s="6" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H322" s="6"/>
       <c r="I322" s="6"/>
@@ -11488,16 +11426,16 @@
       <c r="A323" s="5"/>
       <c r="B323" s="5"/>
       <c r="C323" s="6" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D323" s="6" t="s">
         <v>1083</v>
       </c>
-      <c r="D323" s="6" t="s">
+      <c r="E323" s="6" t="s">
         <v>1084</v>
       </c>
-      <c r="E323" s="6" t="s">
-        <v>1085</v>
-      </c>
       <c r="F323" s="6" t="s">
-        <v>712</v>
+        <v>982</v>
       </c>
       <c r="G323" s="6" t="s">
         <v>15</v>
@@ -11509,16 +11447,16 @@
       <c r="A324" s="5"/>
       <c r="B324" s="5"/>
       <c r="C324" s="6" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D324" s="6" t="s">
         <v>1086</v>
       </c>
-      <c r="D324" s="6" t="s">
+      <c r="E324" s="6" t="s">
         <v>1087</v>
       </c>
-      <c r="E324" s="6" t="s">
-        <v>1088</v>
-      </c>
       <c r="F324" s="6" t="s">
-        <v>712</v>
+        <v>982</v>
       </c>
       <c r="G324" s="6" t="s">
         <v>15</v>
@@ -11530,16 +11468,16 @@
       <c r="A325" s="5"/>
       <c r="B325" s="5"/>
       <c r="C325" s="6" t="s">
+        <v>1088</v>
+      </c>
+      <c r="D325" s="6" t="s">
         <v>1089</v>
       </c>
-      <c r="D325" s="6" t="s">
+      <c r="E325" s="6" t="s">
         <v>1090</v>
       </c>
-      <c r="E325" s="6" t="s">
-        <v>1091</v>
-      </c>
       <c r="F325" s="6" t="s">
-        <v>89</v>
+        <v>166</v>
       </c>
       <c r="G325" s="6" t="s">
         <v>30</v>
@@ -11551,16 +11489,16 @@
       <c r="A326" s="5"/>
       <c r="B326" s="5"/>
       <c r="C326" s="6" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D326" s="6" t="s">
         <v>1092</v>
       </c>
-      <c r="D326" s="6" t="s">
+      <c r="E326" s="6" t="s">
         <v>1093</v>
       </c>
-      <c r="E326" s="6" t="s">
-        <v>1094</v>
-      </c>
       <c r="F326" s="6" t="s">
-        <v>89</v>
+        <v>166</v>
       </c>
       <c r="G326" s="6" t="s">
         <v>30</v>
@@ -11573,19 +11511,19 @@
         <v>55</v>
       </c>
       <c r="B327" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C327" s="4" t="s">
         <v>1095</v>
       </c>
-      <c r="C327" s="4" t="s">
+      <c r="D327" s="4" t="s">
         <v>1096</v>
       </c>
-      <c r="D327" s="4" t="s">
+      <c r="E327" s="4" t="s">
         <v>1097</v>
       </c>
-      <c r="E327" s="4" t="s">
-        <v>1098</v>
-      </c>
       <c r="F327" s="4" t="s">
-        <v>983</v>
+        <v>361</v>
       </c>
       <c r="G327" s="4" t="s">
         <v>15</v>
@@ -11601,16 +11539,16 @@
       <c r="A328" s="3"/>
       <c r="B328" s="3"/>
       <c r="C328" s="4" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D328" s="4" t="s">
         <v>1099</v>
       </c>
-      <c r="D328" s="4" t="s">
+      <c r="E328" s="4" t="s">
         <v>1100</v>
       </c>
-      <c r="E328" s="4" t="s">
-        <v>1101</v>
-      </c>
       <c r="F328" s="4" t="s">
-        <v>983</v>
+        <v>340</v>
       </c>
       <c r="G328" s="4" t="s">
         <v>15</v>
@@ -11622,16 +11560,16 @@
       <c r="A329" s="3"/>
       <c r="B329" s="3"/>
       <c r="C329" s="4" t="s">
+        <v>1101</v>
+      </c>
+      <c r="D329" s="4" t="s">
         <v>1102</v>
       </c>
-      <c r="D329" s="4" t="s">
+      <c r="E329" s="4" t="s">
         <v>1103</v>
       </c>
-      <c r="E329" s="4" t="s">
-        <v>1104</v>
-      </c>
       <c r="F329" s="4" t="s">
-        <v>983</v>
+        <v>361</v>
       </c>
       <c r="G329" s="4" t="s">
         <v>15</v>
@@ -11643,19 +11581,19 @@
       <c r="A330" s="3"/>
       <c r="B330" s="3"/>
       <c r="C330" s="4" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D330" s="4" t="s">
         <v>1105</v>
       </c>
-      <c r="D330" s="4" t="s">
+      <c r="E330" s="4" t="s">
         <v>1106</v>
       </c>
-      <c r="E330" s="4" t="s">
-        <v>1107</v>
-      </c>
       <c r="F330" s="4" t="s">
-        <v>983</v>
+        <v>368</v>
       </c>
       <c r="G330" s="4" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H330" s="4"/>
       <c r="I330" s="4"/>
@@ -11664,16 +11602,16 @@
       <c r="A331" s="3"/>
       <c r="B331" s="3"/>
       <c r="C331" s="4" t="s">
+        <v>1107</v>
+      </c>
+      <c r="D331" s="4" t="s">
         <v>1108</v>
       </c>
-      <c r="D331" s="4" t="s">
+      <c r="E331" s="4" t="s">
         <v>1109</v>
       </c>
-      <c r="E331" s="4" t="s">
-        <v>1110</v>
-      </c>
       <c r="F331" s="4" t="s">
-        <v>187</v>
+        <v>368</v>
       </c>
       <c r="G331" s="4" t="s">
         <v>30</v>
@@ -11685,19 +11623,19 @@
       <c r="A332" s="3"/>
       <c r="B332" s="3"/>
       <c r="C332" s="4" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D332" s="4" t="s">
         <v>1111</v>
       </c>
-      <c r="D332" s="4" t="s">
+      <c r="E332" s="4" t="s">
         <v>1112</v>
       </c>
-      <c r="E332" s="4" t="s">
-        <v>1113</v>
-      </c>
       <c r="F332" s="4" t="s">
-        <v>187</v>
+        <v>340</v>
       </c>
       <c r="G332" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H332" s="4"/>
       <c r="I332" s="4"/>
@@ -11707,22 +11645,22 @@
         <v>56</v>
       </c>
       <c r="B333" s="5" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C333" s="6" t="s">
         <v>1114</v>
       </c>
-      <c r="C333" s="6" t="s">
+      <c r="D333" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="D333" s="6" t="s">
+      <c r="E333" s="6" t="s">
         <v>1116</v>
       </c>
-      <c r="E333" s="6" t="s">
-        <v>1117</v>
-      </c>
       <c r="F333" s="6" t="s">
-        <v>382</v>
+        <v>217</v>
       </c>
       <c r="G333" s="6" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H333" s="6" t="s">
         <v>16</v>
@@ -11735,19 +11673,19 @@
       <c r="A334" s="5"/>
       <c r="B334" s="5"/>
       <c r="C334" s="6" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D334" s="6" t="s">
         <v>1118</v>
       </c>
-      <c r="D334" s="6" t="s">
+      <c r="E334" s="6" t="s">
         <v>1119</v>
       </c>
-      <c r="E334" s="6" t="s">
-        <v>1120</v>
-      </c>
       <c r="F334" s="6" t="s">
-        <v>361</v>
+        <v>217</v>
       </c>
       <c r="G334" s="6" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H334" s="6"/>
       <c r="I334" s="6"/>
@@ -11756,19 +11694,19 @@
       <c r="A335" s="5"/>
       <c r="B335" s="5"/>
       <c r="C335" s="6" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D335" s="6" t="s">
         <v>1121</v>
       </c>
-      <c r="D335" s="6" t="s">
+      <c r="E335" s="6" t="s">
         <v>1122</v>
       </c>
-      <c r="E335" s="6" t="s">
-        <v>1123</v>
-      </c>
       <c r="F335" s="6" t="s">
-        <v>382</v>
+        <v>982</v>
       </c>
       <c r="G335" s="6" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H335" s="6"/>
       <c r="I335" s="6"/>
@@ -11777,16 +11715,16 @@
       <c r="A336" s="5"/>
       <c r="B336" s="5"/>
       <c r="C336" s="6" t="s">
+        <v>1123</v>
+      </c>
+      <c r="D336" s="6" t="s">
         <v>1124</v>
       </c>
-      <c r="D336" s="6" t="s">
+      <c r="E336" s="6" t="s">
         <v>1125</v>
       </c>
-      <c r="E336" s="6" t="s">
-        <v>1126</v>
-      </c>
       <c r="F336" s="6" t="s">
-        <v>389</v>
+        <v>982</v>
       </c>
       <c r="G336" s="6" t="s">
         <v>30</v>
@@ -11798,19 +11736,19 @@
       <c r="A337" s="5"/>
       <c r="B337" s="5"/>
       <c r="C337" s="6" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D337" s="6" t="s">
         <v>1127</v>
       </c>
-      <c r="D337" s="6" t="s">
+      <c r="E337" s="6" t="s">
         <v>1128</v>
       </c>
-      <c r="E337" s="6" t="s">
-        <v>1129</v>
-      </c>
       <c r="F337" s="6" t="s">
-        <v>389</v>
+        <v>99</v>
       </c>
       <c r="G337" s="6" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H337" s="6"/>
       <c r="I337" s="6"/>
@@ -11819,16 +11757,16 @@
       <c r="A338" s="5"/>
       <c r="B338" s="5"/>
       <c r="C338" s="6" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D338" s="6" t="s">
         <v>1130</v>
       </c>
-      <c r="D338" s="6" t="s">
+      <c r="E338" s="6" t="s">
         <v>1131</v>
       </c>
-      <c r="E338" s="6" t="s">
-        <v>1132</v>
-      </c>
       <c r="F338" s="6" t="s">
-        <v>361</v>
+        <v>99</v>
       </c>
       <c r="G338" s="6" t="s">
         <v>15</v>
@@ -11841,22 +11779,22 @@
         <v>57</v>
       </c>
       <c r="B339" s="3" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C339" s="4" t="s">
         <v>1133</v>
       </c>
-      <c r="C339" s="4" t="s">
+      <c r="D339" s="4" t="s">
         <v>1134</v>
       </c>
-      <c r="D339" s="4" t="s">
+      <c r="E339" s="4" t="s">
         <v>1135</v>
       </c>
-      <c r="E339" s="4" t="s">
-        <v>1136</v>
-      </c>
       <c r="F339" s="4" t="s">
-        <v>238</v>
+        <v>368</v>
       </c>
       <c r="G339" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H339" s="4" t="s">
         <v>16</v>
@@ -11869,19 +11807,19 @@
       <c r="A340" s="3"/>
       <c r="B340" s="3"/>
       <c r="C340" s="4" t="s">
+        <v>1136</v>
+      </c>
+      <c r="D340" s="4" t="s">
         <v>1137</v>
       </c>
-      <c r="D340" s="4" t="s">
+      <c r="E340" s="4" t="s">
         <v>1138</v>
       </c>
-      <c r="E340" s="4" t="s">
-        <v>1139</v>
-      </c>
       <c r="F340" s="4" t="s">
-        <v>238</v>
+        <v>368</v>
       </c>
       <c r="G340" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H340" s="4"/>
       <c r="I340" s="4"/>
@@ -11890,16 +11828,16 @@
       <c r="A341" s="3"/>
       <c r="B341" s="3"/>
       <c r="C341" s="4" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D341" s="4" t="s">
         <v>1140</v>
       </c>
-      <c r="D341" s="4" t="s">
+      <c r="E341" s="4" t="s">
         <v>1141</v>
       </c>
-      <c r="E341" s="4" t="s">
-        <v>1142</v>
-      </c>
       <c r="F341" s="4" t="s">
-        <v>983</v>
+        <v>132</v>
       </c>
       <c r="G341" s="4" t="s">
         <v>30</v>
@@ -11911,16 +11849,16 @@
       <c r="A342" s="3"/>
       <c r="B342" s="3"/>
       <c r="C342" s="4" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D342" s="4" t="s">
         <v>1143</v>
       </c>
-      <c r="D342" s="4" t="s">
+      <c r="E342" s="4" t="s">
         <v>1144</v>
       </c>
-      <c r="E342" s="4" t="s">
-        <v>1145</v>
-      </c>
       <c r="F342" s="4" t="s">
-        <v>983</v>
+        <v>132</v>
       </c>
       <c r="G342" s="4" t="s">
         <v>30</v>
@@ -11932,19 +11870,19 @@
       <c r="A343" s="3"/>
       <c r="B343" s="3"/>
       <c r="C343" s="4" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D343" s="4" t="s">
         <v>1146</v>
       </c>
-      <c r="D343" s="4" t="s">
+      <c r="E343" s="4" t="s">
         <v>1147</v>
       </c>
-      <c r="E343" s="4" t="s">
-        <v>1148</v>
-      </c>
       <c r="F343" s="4" t="s">
-        <v>99</v>
+        <v>132</v>
       </c>
       <c r="G343" s="4" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H343" s="4"/>
       <c r="I343" s="4"/>
@@ -11953,19 +11891,19 @@
       <c r="A344" s="3"/>
       <c r="B344" s="3"/>
       <c r="C344" s="4" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D344" s="4" t="s">
         <v>1149</v>
       </c>
-      <c r="D344" s="4" t="s">
+      <c r="E344" s="4" t="s">
         <v>1150</v>
       </c>
-      <c r="E344" s="4" t="s">
-        <v>1151</v>
-      </c>
       <c r="F344" s="4" t="s">
-        <v>99</v>
+        <v>132</v>
       </c>
       <c r="G344" s="4" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H344" s="4"/>
       <c r="I344" s="4"/>
@@ -11975,19 +11913,19 @@
         <v>58</v>
       </c>
       <c r="B345" s="5" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C345" s="6" t="s">
         <v>1152</v>
       </c>
-      <c r="C345" s="6" t="s">
+      <c r="D345" s="6" t="s">
         <v>1153</v>
       </c>
-      <c r="D345" s="6" t="s">
+      <c r="E345" s="6" t="s">
         <v>1154</v>
       </c>
-      <c r="E345" s="6" t="s">
-        <v>1155</v>
-      </c>
       <c r="F345" s="6" t="s">
-        <v>389</v>
+        <v>256</v>
       </c>
       <c r="G345" s="6" t="s">
         <v>15</v>
@@ -12003,19 +11941,19 @@
       <c r="A346" s="5"/>
       <c r="B346" s="5"/>
       <c r="C346" s="6" t="s">
+        <v>1155</v>
+      </c>
+      <c r="D346" s="6" t="s">
         <v>1156</v>
       </c>
-      <c r="D346" s="6" t="s">
+      <c r="E346" s="6" t="s">
         <v>1157</v>
       </c>
-      <c r="E346" s="6" t="s">
-        <v>1158</v>
-      </c>
       <c r="F346" s="6" t="s">
-        <v>389</v>
+        <v>256</v>
       </c>
       <c r="G346" s="6" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H346" s="6"/>
       <c r="I346" s="6"/>
@@ -12024,16 +11962,16 @@
       <c r="A347" s="5"/>
       <c r="B347" s="5"/>
       <c r="C347" s="6" t="s">
+        <v>1158</v>
+      </c>
+      <c r="D347" s="6" t="s">
         <v>1159</v>
       </c>
-      <c r="D347" s="6" t="s">
+      <c r="E347" s="6" t="s">
         <v>1160</v>
       </c>
-      <c r="E347" s="6" t="s">
-        <v>1161</v>
-      </c>
       <c r="F347" s="6" t="s">
-        <v>153</v>
+        <v>66</v>
       </c>
       <c r="G347" s="6" t="s">
         <v>30</v>
@@ -12045,19 +11983,19 @@
       <c r="A348" s="5"/>
       <c r="B348" s="5"/>
       <c r="C348" s="6" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D348" s="6" t="s">
         <v>1162</v>
       </c>
-      <c r="D348" s="6" t="s">
+      <c r="E348" s="6" t="s">
         <v>1163</v>
       </c>
-      <c r="E348" s="6" t="s">
-        <v>1164</v>
-      </c>
       <c r="F348" s="6" t="s">
-        <v>153</v>
+        <v>256</v>
       </c>
       <c r="G348" s="6" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H348" s="6"/>
       <c r="I348" s="6"/>
@@ -12066,19 +12004,19 @@
       <c r="A349" s="5"/>
       <c r="B349" s="5"/>
       <c r="C349" s="6" t="s">
+        <v>1164</v>
+      </c>
+      <c r="D349" s="6" t="s">
         <v>1165</v>
       </c>
-      <c r="D349" s="6" t="s">
+      <c r="E349" s="6" t="s">
         <v>1166</v>
       </c>
-      <c r="E349" s="6" t="s">
-        <v>1167</v>
-      </c>
       <c r="F349" s="6" t="s">
-        <v>153</v>
+        <v>82</v>
       </c>
       <c r="G349" s="6" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H349" s="6"/>
       <c r="I349" s="6"/>
@@ -12087,19 +12025,19 @@
       <c r="A350" s="5"/>
       <c r="B350" s="5"/>
       <c r="C350" s="6" t="s">
+        <v>1167</v>
+      </c>
+      <c r="D350" s="6" t="s">
         <v>1168</v>
       </c>
-      <c r="D350" s="6" t="s">
+      <c r="E350" s="6" t="s">
         <v>1169</v>
       </c>
-      <c r="E350" s="6" t="s">
+      <c r="F350" s="6" t="s">
         <v>1170</v>
       </c>
-      <c r="F350" s="6" t="s">
-        <v>153</v>
-      </c>
       <c r="G350" s="6" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H350" s="6"/>
       <c r="I350" s="6"/>
@@ -12121,7 +12059,7 @@
         <v>1174</v>
       </c>
       <c r="F351" s="4" t="s">
-        <v>277</v>
+        <v>66</v>
       </c>
       <c r="G351" s="4" t="s">
         <v>15</v>
@@ -12146,10 +12084,10 @@
         <v>1177</v>
       </c>
       <c r="F352" s="4" t="s">
-        <v>277</v>
+        <v>66</v>
       </c>
       <c r="G352" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H352" s="4"/>
       <c r="I352" s="4"/>
@@ -12167,10 +12105,10 @@
         <v>1180</v>
       </c>
       <c r="F353" s="4" t="s">
-        <v>66</v>
+        <v>913</v>
       </c>
       <c r="G353" s="4" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H353" s="4"/>
       <c r="I353" s="4"/>
@@ -12188,7 +12126,7 @@
         <v>1183</v>
       </c>
       <c r="F354" s="4" t="s">
-        <v>277</v>
+        <v>913</v>
       </c>
       <c r="G354" s="4" t="s">
         <v>15</v>
@@ -12209,10 +12147,10 @@
         <v>1186</v>
       </c>
       <c r="F355" s="4" t="s">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="G355" s="4" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H355" s="4"/>
       <c r="I355" s="4"/>
@@ -12230,10 +12168,10 @@
         <v>1189</v>
       </c>
       <c r="F356" s="4" t="s">
-        <v>1190</v>
+        <v>114</v>
       </c>
       <c r="G356" s="4" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H356" s="4"/>
       <c r="I356" s="4"/>
@@ -12243,19 +12181,19 @@
         <v>60</v>
       </c>
       <c r="B357" s="5" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C357" s="6" t="s">
         <v>1191</v>
       </c>
-      <c r="C357" s="6" t="s">
+      <c r="D357" s="6" t="s">
         <v>1192</v>
       </c>
-      <c r="D357" s="6" t="s">
+      <c r="E357" s="6" t="s">
         <v>1193</v>
       </c>
-      <c r="E357" s="6" t="s">
-        <v>1194</v>
-      </c>
       <c r="F357" s="6" t="s">
-        <v>66</v>
+        <v>480</v>
       </c>
       <c r="G357" s="6" t="s">
         <v>15</v>
@@ -12271,16 +12209,16 @@
       <c r="A358" s="5"/>
       <c r="B358" s="5"/>
       <c r="C358" s="6" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D358" s="6" t="s">
         <v>1195</v>
       </c>
-      <c r="D358" s="6" t="s">
+      <c r="E358" s="6" t="s">
         <v>1196</v>
       </c>
-      <c r="E358" s="6" t="s">
-        <v>1197</v>
-      </c>
       <c r="F358" s="6" t="s">
-        <v>66</v>
+        <v>480</v>
       </c>
       <c r="G358" s="6" t="s">
         <v>15</v>
@@ -12292,19 +12230,19 @@
       <c r="A359" s="5"/>
       <c r="B359" s="5"/>
       <c r="C359" s="6" t="s">
+        <v>1197</v>
+      </c>
+      <c r="D359" s="6" t="s">
         <v>1198</v>
       </c>
-      <c r="D359" s="6" t="s">
+      <c r="E359" s="6" t="s">
         <v>1199</v>
       </c>
-      <c r="E359" s="6" t="s">
-        <v>1200</v>
-      </c>
       <c r="F359" s="6" t="s">
-        <v>914</v>
+        <v>451</v>
       </c>
       <c r="G359" s="6" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H359" s="6"/>
       <c r="I359" s="6"/>
@@ -12313,19 +12251,19 @@
       <c r="A360" s="5"/>
       <c r="B360" s="5"/>
       <c r="C360" s="6" t="s">
+        <v>1200</v>
+      </c>
+      <c r="D360" s="6" t="s">
         <v>1201</v>
       </c>
-      <c r="D360" s="6" t="s">
+      <c r="E360" s="6" t="s">
         <v>1202</v>
       </c>
-      <c r="E360" s="6" t="s">
-        <v>1203</v>
-      </c>
       <c r="F360" s="6" t="s">
-        <v>914</v>
+        <v>128</v>
       </c>
       <c r="G360" s="6" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H360" s="6"/>
       <c r="I360" s="6"/>
@@ -12334,16 +12272,16 @@
       <c r="A361" s="5"/>
       <c r="B361" s="5"/>
       <c r="C361" s="6" t="s">
+        <v>1203</v>
+      </c>
+      <c r="D361" s="6" t="s">
         <v>1204</v>
       </c>
-      <c r="D361" s="6" t="s">
+      <c r="E361" s="6" t="s">
         <v>1205</v>
       </c>
-      <c r="E361" s="6" t="s">
-        <v>1206</v>
-      </c>
       <c r="F361" s="6" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="G361" s="6" t="s">
         <v>30</v>
@@ -12355,159 +12293,25 @@
       <c r="A362" s="5"/>
       <c r="B362" s="5"/>
       <c r="C362" s="6" t="s">
+        <v>1206</v>
+      </c>
+      <c r="D362" s="6" t="s">
         <v>1207</v>
       </c>
-      <c r="D362" s="6" t="s">
+      <c r="E362" s="6" t="s">
         <v>1208</v>
       </c>
-      <c r="E362" s="6" t="s">
-        <v>1209</v>
-      </c>
       <c r="F362" s="6" t="s">
-        <v>135</v>
+        <v>480</v>
       </c>
       <c r="G362" s="6" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H362" s="6"/>
       <c r="I362" s="6"/>
     </row>
-    <row r="363" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A363" s="3">
-        <v>61</v>
-      </c>
-      <c r="B363" s="3" t="s">
-        <v>1210</v>
-      </c>
-      <c r="C363" s="4" t="s">
-        <v>1211</v>
-      </c>
-      <c r="D363" s="4" t="s">
-        <v>1212</v>
-      </c>
-      <c r="E363" s="4" t="s">
-        <v>1213</v>
-      </c>
-      <c r="F363" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="G363" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H363" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I363" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="364" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A364" s="3"/>
-      <c r="B364" s="3"/>
-      <c r="C364" s="4" t="s">
-        <v>1214</v>
-      </c>
-      <c r="D364" s="4" t="s">
-        <v>1215</v>
-      </c>
-      <c r="E364" s="4" t="s">
-        <v>1216</v>
-      </c>
-      <c r="F364" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="G364" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H364" s="4"/>
-      <c r="I364" s="4"/>
-    </row>
-    <row r="365" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A365" s="3"/>
-      <c r="B365" s="3"/>
-      <c r="C365" s="4" t="s">
-        <v>1217</v>
-      </c>
-      <c r="D365" s="4" t="s">
-        <v>1218</v>
-      </c>
-      <c r="E365" s="4" t="s">
-        <v>1219</v>
-      </c>
-      <c r="F365" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="G365" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H365" s="4"/>
-      <c r="I365" s="4"/>
-    </row>
-    <row r="366" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A366" s="3"/>
-      <c r="B366" s="3"/>
-      <c r="C366" s="4" t="s">
-        <v>1220</v>
-      </c>
-      <c r="D366" s="4" t="s">
-        <v>1221</v>
-      </c>
-      <c r="E366" s="4" t="s">
-        <v>1222</v>
-      </c>
-      <c r="F366" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="G366" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H366" s="4"/>
-      <c r="I366" s="4"/>
-    </row>
-    <row r="367" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A367" s="3"/>
-      <c r="B367" s="3"/>
-      <c r="C367" s="4" t="s">
-        <v>1223</v>
-      </c>
-      <c r="D367" s="4" t="s">
-        <v>1224</v>
-      </c>
-      <c r="E367" s="4" t="s">
-        <v>1225</v>
-      </c>
-      <c r="F367" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="G367" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H367" s="4"/>
-      <c r="I367" s="4"/>
-    </row>
-    <row r="368" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A368" s="3"/>
-      <c r="B368" s="3"/>
-      <c r="C368" s="4" t="s">
-        <v>1226</v>
-      </c>
-      <c r="D368" s="4" t="s">
-        <v>1227</v>
-      </c>
-      <c r="E368" s="4" t="s">
-        <v>1228</v>
-      </c>
-      <c r="F368" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="G368" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H368" s="4"/>
-      <c r="I368" s="4"/>
-    </row>
   </sheetData>
-  <mergeCells count="245">
+  <mergeCells count="241">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A3:A8"/>
     <mergeCell ref="B3:B8"/>
@@ -12749,10 +12553,6 @@
     <mergeCell ref="B357:B362"/>
     <mergeCell ref="H357:H362"/>
     <mergeCell ref="I357:I362"/>
-    <mergeCell ref="A363:A368"/>
-    <mergeCell ref="B363:B368"/>
-    <mergeCell ref="H363:H368"/>
-    <mergeCell ref="I363:I368"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
